--- a/セリフ編集/キャラタイプ別/クール×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/クール×ノーマル.xlsx
@@ -318,7 +318,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H198"/>
+  <dimension ref="A1:H283"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1656,7 +1656,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.normal.cool[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.normal.cool[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1666,12 +1666,12 @@
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal.cool[1]</t>
+          <t xml:space="preserve">ahead.normal.cool[1]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
@@ -1681,14 +1681,14 @@
       </c>
       <c r="F42" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……今日は負けた。だが……終わらない</t>
+          <t xml:space="preserve">……済んだ話だ。まだ気にする方がどうかしてる</t>
         </is>
       </c>
     </row>
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.normal.cool[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.normal.cool[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.cool[1]</t>
+          <t xml:space="preserve">behind.normal.cool[1]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
@@ -1713,14 +1713,14 @@
       </c>
       <c r="F43" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……決着だ。消えろ</t>
+          <t xml:space="preserve">……決着はついた。納得したとは、言ってない</t>
         </is>
       </c>
     </row>
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.normal.cool[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.normal.cool[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.cool[1]</t>
+          <t xml:space="preserve">loser.normal.cool[1]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
@@ -1745,14 +1745,14 @@
       </c>
       <c r="F44" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……認めている。これからも、共に</t>
+          <t xml:space="preserve">……今日は負けた。だが……終わらない</t>
         </is>
       </c>
     </row>
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.normal.cool[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.normal.cool[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal.cool[1]</t>
+          <t xml:space="preserve">winner.normal.cool[1]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="2">
@@ -1777,14 +1777,14 @@
       </c>
       <c r="F45" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……逃がさない。終わらせる</t>
+          <t xml:space="preserve">……決着だ。消えろ</t>
         </is>
       </c>
     </row>
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.normal.cool[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.normal.cool[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal.cool[1]</t>
+          <t xml:space="preserve">winner.normal.cool[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1809,14 +1809,14 @@
       </c>
       <c r="F46" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……来い。迎え撃つ</t>
+          <t xml:space="preserve">……認めている。これからも、共に</t>
         </is>
       </c>
     </row>
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.normal.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.normal.cool[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
         </is>
       </c>
       <c r="D47" t="inlineStr" s="12">
@@ -1841,14 +1841,14 @@
       </c>
       <c r="F47" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……来た。この日が</t>
+          <t xml:space="preserve">……逃がさない。終わらせる</t>
         </is>
       </c>
     </row>
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.normal.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.normal.cool[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
         </is>
       </c>
       <c r="D48" t="inlineStr" s="12">
@@ -1873,14 +1873,14 @@
       </c>
       <c r="F48" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ああ</t>
+          <t xml:space="preserve">……来い。迎え撃つ</t>
         </is>
       </c>
     </row>
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.normal.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.normal.cool[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
         </is>
       </c>
       <c r="D49" t="inlineStr" s="12">
@@ -1905,14 +1905,14 @@
       </c>
       <c r="F49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……決着をつける</t>
+          <t xml:space="preserve">……来た。この日が</t>
         </is>
       </c>
     </row>
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.normal.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.normal.cool[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
         </is>
       </c>
       <c r="D50" t="inlineStr" s="12">
@@ -1937,14 +1937,14 @@
       </c>
       <c r="F50" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……来い</t>
+          <t xml:space="preserve">……ああ</t>
         </is>
       </c>
     </row>
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.normal.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.normal.cool[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.normal.cool[1]</t>
+          <t xml:space="preserve">attacker.normal.cool[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -1969,14 +1969,14 @@
       </c>
       <c r="F51" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……終わらせに来た</t>
+          <t xml:space="preserve">……決着をつける</t>
         </is>
       </c>
     </row>
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.normal.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.normal.cool[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.normal.cool[1]</t>
+          <t xml:space="preserve">defender.normal.cool[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -2001,14 +2001,14 @@
       </c>
       <c r="F52" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……わかっている</t>
+          <t xml:space="preserve">……来い</t>
         </is>
       </c>
     </row>
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.normal.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.normal.cool[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
         </is>
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.normal.cool[1]</t>
+          <t xml:space="preserve">fateAttacker.normal.cool[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -2033,14 +2033,14 @@
       </c>
       <c r="F53" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は、ない。次こそ倒す</t>
+          <t xml:space="preserve">……終わらせに来た</t>
         </is>
       </c>
     </row>
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.normal.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.normal.cool[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
         </is>
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.normal.cool[1]</t>
+          <t xml:space="preserve">fateDefender.normal.cool[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2065,14 +2065,14 @@
       </c>
       <c r="F54" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだだ</t>
+          <t xml:space="preserve">……わかっている</t>
         </is>
       </c>
     </row>
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.normal.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.normal.cool[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2082,12 +2082,12 @@
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.normal.cool[1]</t>
+          <t xml:space="preserve">loserLines.normal.cool[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2097,14 +2097,14 @@
       </c>
       <c r="F55" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……敵わなかった。……だが、終わりではない</t>
+          <t xml:space="preserve">……次は、ない。次こそ倒す</t>
         </is>
       </c>
     </row>
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.normal.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.normal.cool[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.normal.cool[1]</t>
+          <t xml:space="preserve">winnerLines.normal.cool[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2129,14 +2129,14 @@
       </c>
       <c r="F56" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一つ、答えが出た。……だが、まだ終わらない</t>
+          <t xml:space="preserve">……まだだ</t>
         </is>
       </c>
     </row>
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.normal.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.normal.cool[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal.cool[1]</t>
+          <t xml:space="preserve">fateLoser.normal.cool[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2161,14 +2161,14 @@
       </c>
       <c r="F57" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負けた。……だが、終わりではない</t>
+          <t xml:space="preserve">……敵わなかった。……だが、終わりではない</t>
         </is>
       </c>
     </row>
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.normal.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.normal.cool[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.cool[1]</t>
+          <t xml:space="preserve">fateWinner.normal.cool[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -2193,14 +2193,14 @@
       </c>
       <c r="F58" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一つ、片がついた。……だが、これで終わりではない</t>
+          <t xml:space="preserve">……一つ、答えが出た。……だが、まだ終わらない</t>
         </is>
       </c>
     </row>
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.normal.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.normal.cool[1]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2210,12 +2210,12 @@
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.normal.cool[1]</t>
+          <t xml:space="preserve">loser.normal.cool[1]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
@@ -2225,14 +2225,14 @@
       </c>
       <c r="F59" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（信じられないという表情で立ち尽くす）</t>
+          <t xml:space="preserve">……負けた。……だが、終わりではない</t>
         </is>
       </c>
     </row>
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.normal.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.normal.cool[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.normal.cool[1]</t>
+          <t xml:space="preserve">winner.normal.cool[1]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
@@ -2257,14 +2257,14 @@
       </c>
       <c r="F60" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……証明した</t>
+          <t xml:space="preserve">……一つ、片がついた。……だが、これで終わりではない</t>
         </is>
       </c>
     </row>
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.normal.cool[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.normal.cool[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2274,12 +2274,12 @@
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
         </is>
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.normal.cool[1]</t>
+          <t xml:space="preserve">loserLines.normal.cool[1]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
@@ -2289,14 +2289,14 @@
       </c>
       <c r="F61" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameB}の表情が変わった。「……もういい。覚悟は決めた」</t>
+          <t xml:space="preserve">………（信じられないという表情で立ち尽くす）</t>
         </is>
       </c>
     </row>
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.cool_normal.lose[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.normal.cool[1]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2306,29 +2306,29 @@
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
         </is>
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_normal.lose[1]</t>
+          <t xml:space="preserve">winnerLines.normal.cool[1]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
         </is>
       </c>
       <c r="F62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負けました。申し訳ない。</t>
+          <t xml:space="preserve">……証明した</t>
         </is>
       </c>
     </row>
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.cool_normal.lose[2]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.normal.cool[1]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2338,29 +2338,29 @@
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
         </is>
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_normal.lose[2]</t>
+          <t xml:space="preserve">awakening.normal.cool[1]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
         </is>
       </c>
       <c r="F63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……完敗です。悔しい。</t>
+          <t xml:space="preserve">{nameB}の表情が変わった。「……もういい。覚悟は決めた」</t>
         </is>
       </c>
     </row>
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.cool_normal.lose[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.cool_normal.lose[1]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="D64" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_normal.lose[3]</t>
+          <t xml:space="preserve">cool_normal.lose[1]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr" s="2">
@@ -2385,14 +2385,14 @@
       </c>
       <c r="F64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝てませんでした。次は、勝ちます。</t>
+          <t xml:space="preserve">……負けました。申し訳ない。</t>
         </is>
       </c>
     </row>
     <row r="65" ht="40" customHeight="1">
       <c r="A65" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.cool_normal.petition[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.cool_normal.lose[2]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="D65" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_normal.petition[1]</t>
+          <t xml:space="preserve">cool_normal.lose[2]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr" s="2">
@@ -2417,14 +2417,14 @@
       </c>
       <c r="F65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……社長。あの人と、やらせてください。</t>
+          <t xml:space="preserve">……完敗です。悔しい。</t>
         </is>
       </c>
     </row>
     <row r="66" ht="40" customHeight="1">
       <c r="A66" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.cool_normal.petition[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.cool_normal.lose[3]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="D66" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_normal.petition[2]</t>
+          <t xml:space="preserve">cool_normal.lose[3]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr" s="2">
@@ -2449,14 +2449,14 @@
       </c>
       <c r="F66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……頼みがあります。あの人と、やりたい。</t>
+          <t xml:space="preserve">……勝てませんでした。次は、勝ちます。</t>
         </is>
       </c>
     </row>
     <row r="67" ht="40" customHeight="1">
       <c r="A67" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.cool_normal.petition[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.cool_normal.petition[1]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="D67" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_normal.petition[3]</t>
+          <t xml:space="preserve">cool_normal.petition[1]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr" s="2">
@@ -2481,14 +2481,14 @@
       </c>
       <c r="F67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの人だ。あの人と、やらせてほしい。</t>
+          <t xml:space="preserve">……社長。あの人と、やらせてください。</t>
         </is>
       </c>
     </row>
     <row r="68" ht="40" customHeight="1">
       <c r="A68" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.cool_normal.sendoff[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.cool_normal.petition[2]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="D68" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_normal.sendoff[1]</t>
+          <t xml:space="preserve">cool_normal.petition[2]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr" s="2">
@@ -2513,14 +2513,14 @@
       </c>
       <c r="F68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとうございます。行ってきます。</t>
+          <t xml:space="preserve">……頼みがあります。あの人と、やりたい。</t>
         </is>
       </c>
     </row>
     <row r="69" ht="40" customHeight="1">
       <c r="A69" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.cool_normal.sendoff[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.cool_normal.petition[3]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="D69" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_normal.sendoff[2]</t>
+          <t xml:space="preserve">cool_normal.petition[3]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr" s="2">
@@ -2545,14 +2545,14 @@
       </c>
       <c r="F69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……感謝します。行ってきます。</t>
+          <t xml:space="preserve">……あの人だ。あの人と、やらせてほしい。</t>
         </is>
       </c>
     </row>
     <row r="70" ht="40" customHeight="1">
       <c r="A70" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.cool_normal.sendoff[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.cool_normal.sendoff[1]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="D70" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_normal.sendoff[3]</t>
+          <t xml:space="preserve">cool_normal.sendoff[1]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr" s="2">
@@ -2577,14 +2577,14 @@
       </c>
       <c r="F70" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……無駄にはしません。行ってきます。</t>
+          <t xml:space="preserve">……ありがとうございます。行ってきます。</t>
         </is>
       </c>
     </row>
     <row r="71" ht="40" customHeight="1">
       <c r="A71" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.cool_normal.win[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.cool_normal.sendoff[2]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="D71" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_normal.win[1]</t>
+          <t xml:space="preserve">cool_normal.sendoff[2]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr" s="2">
@@ -2609,14 +2609,14 @@
       </c>
       <c r="F71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝ちました。言ってよかった。</t>
+          <t xml:space="preserve">……感謝します。行ってきます。</t>
         </is>
       </c>
     </row>
     <row r="72" ht="40" customHeight="1">
       <c r="A72" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.cool_normal.win[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.cool_normal.sendoff[3]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="D72" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_normal.win[2]</t>
+          <t xml:space="preserve">cool_normal.sendoff[3]</t>
         </is>
       </c>
       <c r="E72" t="inlineStr" s="2">
@@ -2641,14 +2641,14 @@
       </c>
       <c r="F72" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝ちです。ありがとうございました。</t>
+          <t xml:space="preserve">……無駄にはしません。行ってきます。</t>
         </is>
       </c>
     </row>
     <row r="73" ht="40" customHeight="1">
       <c r="A73" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.cool_normal.win[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.cool_normal.win[1]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="D73" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_normal.win[3]</t>
+          <t xml:space="preserve">cool_normal.win[1]</t>
         </is>
       </c>
       <c r="E73" t="inlineStr" s="2">
@@ -2673,14 +2673,14 @@
       </c>
       <c r="F73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……終わりました。勝ちました。</t>
+          <t xml:space="preserve">……勝ちました。言ってよかった。</t>
         </is>
       </c>
     </row>
     <row r="74" ht="40" customHeight="1">
       <c r="A74" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_normal._accept[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.cool_normal.win[2]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
@@ -2690,12 +2690,12 @@
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D74" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_normal._accept[1]</t>
+          <t xml:space="preserve">cool_normal.win[2]</t>
         </is>
       </c>
       <c r="E74" t="inlineStr" s="2">
@@ -2705,14 +2705,14 @@
       </c>
       <c r="F74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……受ける。理由はいらない。</t>
+          <t xml:space="preserve">……勝ちです。ありがとうございました。</t>
         </is>
       </c>
     </row>
     <row r="75" ht="40" customHeight="1">
       <c r="A75" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_normal._accept[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.cool_normal.win[3]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D75" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_normal._accept[2]</t>
+          <t xml:space="preserve">cool_normal.win[3]</t>
         </is>
       </c>
       <c r="E75" t="inlineStr" s="2">
@@ -2737,14 +2737,14 @@
       </c>
       <c r="F75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……いいだろう。来い。</t>
+          <t xml:space="preserve">……終わりました。勝ちました。</t>
         </is>
       </c>
     </row>
     <row r="76" ht="40" customHeight="1">
       <c r="A76" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_normal._accept[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_normal._accept[1]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="D76" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_normal._accept[3]</t>
+          <t xml:space="preserve">cool_normal._accept[1]</t>
         </is>
       </c>
       <c r="E76" t="inlineStr" s="2">
@@ -2769,14 +2769,14 @@
       </c>
       <c r="F76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……名指しか。応える。</t>
+          <t xml:space="preserve">……受ける。理由はいらない。</t>
         </is>
       </c>
     </row>
     <row r="77" ht="40" customHeight="1">
       <c r="A77" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_normal.draw[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_normal._accept[2]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="D77" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_normal.draw[1]</t>
+          <t xml:space="preserve">cool_normal._accept[2]</t>
         </is>
       </c>
       <c r="E77" t="inlineStr" s="2">
@@ -2801,14 +2801,14 @@
       </c>
       <c r="F77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……決着はつかず、か。</t>
+          <t xml:space="preserve">……いいだろう。来い。</t>
         </is>
       </c>
     </row>
     <row r="78" ht="40" customHeight="1">
       <c r="A78" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_normal.draw[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_normal._accept[3]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="D78" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_normal.draw[2]</t>
+          <t xml:space="preserve">cool_normal._accept[3]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr" s="2">
@@ -2833,14 +2833,14 @@
       </c>
       <c r="F78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ、終わらない。</t>
+          <t xml:space="preserve">……名指しか。応える。</t>
         </is>
       </c>
     </row>
     <row r="79" ht="40" customHeight="1">
       <c r="A79" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_normal.draw[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_normal.draw[1]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="D79" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_normal.draw[3]</t>
+          <t xml:space="preserve">cool_normal.draw[1]</t>
         </is>
       </c>
       <c r="E79" t="inlineStr" s="2">
@@ -2865,14 +2865,14 @@
       </c>
       <c r="F79" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次で決める。</t>
+          <t xml:space="preserve">……決着はつかず、か。</t>
         </is>
       </c>
     </row>
     <row r="80" ht="40" customHeight="1">
       <c r="A80" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_normal.lose[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_normal.draw[2]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="D80" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_normal.lose[1]</t>
+          <t xml:space="preserve">cool_normal.draw[2]</t>
         </is>
       </c>
       <c r="E80" t="inlineStr" s="2">
@@ -2897,14 +2897,14 @@
       </c>
       <c r="F80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……強かった。それだけだ。</t>
+          <t xml:space="preserve">……まだ、終わらない。</t>
         </is>
       </c>
     </row>
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_normal.lose[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_normal.draw[3]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="D81" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_normal.lose[2]</t>
+          <t xml:space="preserve">cool_normal.draw[3]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr" s="2">
@@ -2929,14 +2929,14 @@
       </c>
       <c r="F81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負けた。認める。</t>
+          <t xml:space="preserve">……次で決める。</t>
         </is>
       </c>
     </row>
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_normal.lose[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_normal.lose[1]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="D82" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_normal.lose[3]</t>
+          <t xml:space="preserve">cool_normal.lose[1]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr" s="2">
@@ -2961,14 +2961,14 @@
       </c>
       <c r="F82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……借りだ。返す。</t>
+          <t xml:space="preserve">……強かった。それだけだ。</t>
         </is>
       </c>
     </row>
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_normal.win[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_normal.lose[2]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_normal.win[1]</t>
+          <t xml:space="preserve">cool_normal.lose[2]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr" s="2">
@@ -2993,14 +2993,14 @@
       </c>
       <c r="F83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そこまでだ。</t>
+          <t xml:space="preserve">……負けた。認める。</t>
         </is>
       </c>
     </row>
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_normal.win[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_normal.lose[3]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_normal.win[2]</t>
+          <t xml:space="preserve">cool_normal.lose[3]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr" s="2">
@@ -3025,14 +3025,14 @@
       </c>
       <c r="F84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……届いていない。</t>
+          <t xml:space="preserve">……借りだ。返す。</t>
         </is>
       </c>
     </row>
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_normal.win[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_normal.win[1]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool_normal.win[3]</t>
+          <t xml:space="preserve">cool_normal.win[1]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr" s="2">
@@ -3057,14 +3057,14 @@
       </c>
       <c r="F85" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次はない。</t>
+          <t xml:space="preserve">……そこまでだ。</t>
         </is>
       </c>
     </row>
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.normal.cool[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_normal.win[2]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3074,29 +3074,29 @@
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
         </is>
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.normal.cool[1]</t>
+          <t xml:space="preserve">cool_normal.win[2]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…世話になった。…さよならだ</t>
+          <t xml:space="preserve">……届いていない。</t>
         </is>
       </c>
     </row>
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.normal.cool[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.cool_normal.win[3]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3106,29 +3106,29 @@
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
         </is>
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.normal.cool[1]</t>
+          <t xml:space="preserve">cool_normal.win[3]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…残る。…それだけだ</t>
+          <t xml:space="preserve">……次はない。</t>
         </is>
       </c>
     </row>
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.normal.cool[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.normal.cool[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.normal.cool[1]</t>
+          <t xml:space="preserve">accepted.normal.cool[1]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3153,14 +3153,14 @@
       </c>
       <c r="F88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…止めても無駄だ。…悪く思うな</t>
+          <t xml:space="preserve">…世話になった。…さよならだ</t>
         </is>
       </c>
     </row>
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.normal.cool[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.normal.cool[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.normal.cool[1]</t>
+          <t xml:space="preserve">defended.normal.cool[1]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3185,14 +3185,14 @@
       </c>
       <c r="F89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……残る。…まだやることがある</t>
+          <t xml:space="preserve">…残る。…それだけだ</t>
         </is>
       </c>
     </row>
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.normal.cool[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.normal.cool[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.normal.cool[1]</t>
+          <t xml:space="preserve">defense_failed.normal.cool[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3217,14 +3217,14 @@
       </c>
       <c r="F90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……わかった。…悔いはない</t>
+          <t xml:space="preserve">…止めても無駄だ。…悪く思うな</t>
         </is>
       </c>
     </row>
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.normal.cool[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.normal.cool[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3234,12 +3234,12 @@
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.normal.cool[1]</t>
+          <t xml:space="preserve">former_champ.normal.cool[1]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3249,14 +3249,14 @@
       </c>
       <c r="F91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだだ。…まだ終われない</t>
+          <t xml:space="preserve">……残る。…まだやることがある</t>
         </is>
       </c>
     </row>
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.normal.cool[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.normal.cool[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="C92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.normal.cool[1]</t>
+          <t xml:space="preserve">accept_terminal.normal.cool[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3281,14 +3281,14 @@
       </c>
       <c r="F92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……限界か。…悪くない引き際だ</t>
+          <t xml:space="preserve">……わかった。…悔いはない</t>
         </is>
       </c>
     </row>
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.normal.cool[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">refuse_champ.normal.cool[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3313,14 +3313,14 @@
       </c>
       <c r="F93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（静かにうなずいている）……ここにいる</t>
+          <t xml:space="preserve">……まだだ。…まだ終われない</t>
         </is>
       </c>
     </row>
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.normal.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.normal.cool[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3330,29 +3330,29 @@
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.normal.cool[1]</t>
+          <t xml:space="preserve">A1_champion.normal.cool[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……考えさせてくれ</t>
+          <t xml:space="preserve">……限界か。…悪くない引き際だ</t>
         </is>
       </c>
     </row>
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.normal.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.normal.cool[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3362,29 +3362,29 @@
       </c>
       <c r="C95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.normal.cool[1]</t>
+          <t xml:space="preserve">A2_uncrowned.normal.cool[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……条件次第だ</t>
+          <t xml:space="preserve">…届かなかった。悔いはない</t>
         </is>
       </c>
     </row>
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.normal.cool[2]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3394,29 +3394,29 @@
       </c>
       <c r="C96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">A2_uncrowned.normal.cool[2]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……成長を、実感している</t>
+          <t xml:space="preserve">…夢は叶わなかった。…でも、選んでよかった</t>
         </is>
       </c>
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.normal.cool[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3426,29 +3426,29 @@
       </c>
       <c r="C97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">A3_heel.normal.cool[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……何かが、変わり始めている</t>
+          <t xml:space="preserve">…泣くな。みっともない</t>
         </is>
       </c>
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.normal.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.normal.cool[2]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3458,29 +3458,29 @@
       </c>
       <c r="C98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.normal.cool[1]</t>
+          <t xml:space="preserve">A3_heel.normal.cool[2]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここが、天井か</t>
+          <t xml:space="preserve">…いなくなれば、寂しくなる。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.normal.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.normal.cool[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3490,29 +3490,29 @@
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.normal.cool[1]</t>
+          <t xml:space="preserve">A4_veteran.normal.cool[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一つの壁を、越えた</t>
+          <t xml:space="preserve">…ここが、全部だった</t>
         </is>
       </c>
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.normal.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.normal.cool[2]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3522,29 +3522,29 @@
       </c>
       <c r="C100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.normal.cool[1]</t>
+          <t xml:space="preserve">A4_veteran.normal.cool[2]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……手応えは、ある</t>
+          <t xml:space="preserve">…無駄な時間は、ひとつもない</t>
         </is>
       </c>
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.normal.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.normal.cool[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3554,29 +3554,29 @@
       </c>
       <c r="C101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.normal.cool[1]</t>
+          <t xml:space="preserve">B1_young.normal.cool[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この先に何があるのか。…見てみたい</t>
+          <t xml:space="preserve">…まだ、何も成し遂げていない</t>
         </is>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.normal.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.normal.cool[2]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3586,29 +3586,29 @@
       </c>
       <c r="C102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.normal.cool[1]</t>
+          <t xml:space="preserve">B1_young.normal.cool[2]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……認知されてきた、か</t>
+          <t xml:space="preserve">…ここで終わり。…そんな話があるか</t>
         </is>
       </c>
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.normal.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.normal.cool[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3618,29 +3618,29 @@
       </c>
       <c r="C103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.normal.cool[1]</t>
+          <t xml:space="preserve">B2_prime.normal.cool[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……背負うものが増えた。…それでいい</t>
+          <t xml:space="preserve">…体が、もう言うことを聞かない</t>
         </is>
       </c>
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.normal.cool[2]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3650,29 +3650,29 @@
       </c>
       <c r="C104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">B2_prime.normal.cool[2]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……何のために戦っているのか、見えなくなった</t>
+          <t xml:space="preserve">…これからだった。…悔しい</t>
         </is>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.normal.cool[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3682,29 +3682,29 @@
       </c>
       <c r="C105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">B3_older.normal.cool[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……思い出した。戦う理由を</t>
+          <t xml:space="preserve">…わかっていた。いつか来ると</t>
         </is>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.normal.cool[2]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3714,29 +3714,29 @@
       </c>
       <c r="C106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">B3_older.normal.cool[2]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……戻ってきた。この感覚だ</t>
+          <t xml:space="preserve">…十分だ。よくやった</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.normal.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.normal.cool[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3746,29 +3746,29 @@
       </c>
       <c r="C107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.normal.cool[1]</t>
+          <t xml:space="preserve">B4_champion_injury.normal.cool[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……最近、噛み合わない</t>
+          <t xml:space="preserve">…このベルト、まだ返したくない</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.normal.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.normal.cool[2]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3778,29 +3778,29 @@
       </c>
       <c r="C108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.normal.cool[1]</t>
+          <t xml:space="preserve">B4_champion_injury.normal.cool[2]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう</t>
+          <t xml:space="preserve">…最後の防衛戦。やりたかった</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.normal.cool[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="C109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
         </is>
       </c>
       <c r="D109" t="inlineStr" s="12">
@@ -3820,19 +3820,19 @@
       </c>
       <c r="E109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドーム…ね。来たか</t>
+          <t xml:space="preserve">（静かにうなずいている）……ここにいる</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.cool[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.normal.cool[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3842,29 +3842,29 @@
       </c>
       <c r="C110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">raise_accept.normal.cool[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やることは、変わらない</t>
+          <t xml:space="preserve">…ありがとう。これからも、よろしく</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.cool[3]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.normal.cool[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3874,29 +3874,29 @@
       </c>
       <c r="C111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[3]</t>
+          <t xml:space="preserve">raise_negotiate_accept.normal.cool[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…準備はできてる</t>
+          <t xml:space="preserve">…上がるなら、ありがたい。…やるよ</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.normal.cool[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3906,29 +3906,29 @@
       </c>
       <c r="C112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.normal.cool[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…満員</t>
+          <t xml:space="preserve">…そうか。…分かりました</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.cool[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.normal.cool[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3938,29 +3938,29 @@
       </c>
       <c r="C113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">raise_open.normal.cool[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…客の声が、まだ耳に残ってる</t>
+          <t xml:space="preserve">……考えさせてくれ</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.cool[3]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.normal.cool[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3970,29 +3970,29 @@
       </c>
       <c r="C114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[3]</t>
+          <t xml:space="preserve">raise_refuse.normal.cool[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…忘れない。この景色は</t>
+          <t xml:space="preserve">…そうか。分かった。…少し、残念だ</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.normal.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.normal.cool[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -4002,29 +4002,29 @@
       </c>
       <c r="C115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.normal.cool[1]</t>
+          <t xml:space="preserve">sudden_departure.normal.cool[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そう。わかった</t>
+          <t xml:space="preserve">社長。手短に言う。……辞めます。もう決めた</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.normal.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.normal.cool[2]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4034,29 +4034,29 @@
       </c>
       <c r="C116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.normal.cool[1]</t>
+          <t xml:space="preserve">sudden_departure.normal.cool[2]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（荷物をまとめて帰ろうとしている）</t>
+          <t xml:space="preserve">…世話になった。……でも、もう続けられない</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.normal.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.normal.cool[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4066,29 +4066,29 @@
       </c>
       <c r="C117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.normal.cool[1]</t>
+          <t xml:space="preserve">transfer_listen.normal.cool[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（無言で佇んでいるが、周囲が気を遣って重い空気になっている）</t>
+          <t xml:space="preserve">…聞いてくれるんだ。{record}…新しい場所で、試したい</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.normal.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.normal.cool[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4098,29 +4098,29 @@
       </c>
       <c r="C118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.normal.cool[1]</t>
+          <t xml:space="preserve">transfer_open.normal.cool[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに風景写真と「遠くへ」とだけ投稿。ファンがざわついている）</t>
+          <t xml:space="preserve">…社長。{tenure}…ここを、出ようと思う</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.normal.cool[2]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4130,29 +4130,29 @@
       </c>
       <c r="C119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">transfer_open.normal.cool[2]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よろしく</t>
+          <t xml:space="preserve">…色々、考えた。{tenure}…外でやってみたい</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.cool[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.normal.cool[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4162,29 +4162,29 @@
       </c>
       <c r="C120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">transfer_release.normal.cool[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……全力でやる</t>
+          <t xml:space="preserve">…分かった。{tenure_farewell}{rivalry}…世話になった</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.normal.cool[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4194,29 +4194,29 @@
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.normal.cool[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……すぐ戻る</t>
+          <t xml:space="preserve">…ありがたい。…でも、もう決めた。…ごめん</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.normal.cool[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.normal.cool[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4226,29 +4226,29 @@
       </c>
       <c r="C122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">transfer_retain_success.normal.cool[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……心配はいらない</t>
+          <t xml:space="preserve">…そこまでしてくれるんだ。…分かった。もう少し、やってみる</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.cool[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.normal.cool[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4258,29 +4258,29 @@
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.normal.cool[1]</t>
+          <t xml:space="preserve">start.normal.cool[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よろしく</t>
+          <t xml:space="preserve">……条件次第だ</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.cool[2]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.normal.cool[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4290,29 +4290,29 @@
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.normal.cool[2]</t>
+          <t xml:space="preserve">normal.cool[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……全力でやる</t>
+          <t xml:space="preserve">……成長を、実感している</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.cool[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.normal.cool[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4322,29 +4322,29 @@
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.normal.cool[1]</t>
+          <t xml:space="preserve">normal.cool[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……すぐ戻る</t>
+          <t xml:space="preserve">……何かが、変わり始めている</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.cool[2]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.normal.cool[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4354,29 +4354,29 @@
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.normal.cool[2]</t>
+          <t xml:space="preserve">fresh.normal.cool[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……心配はいらない</t>
+          <t xml:space="preserve">…調子はいい。今なら、何をやっても身につく</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.cool[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.normal.cool[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4386,29 +4386,29 @@
       </c>
       <c r="C127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.normal.cool[1]</t>
+          <t xml:space="preserve">heavy.normal.cool[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そうか。お世話になった</t>
+          <t xml:space="preserve">…体が重い。今日は、何をやっても素通りだ</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.cool[2]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.normal.cool[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4418,29 +4418,29 @@
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.normal.cool[2]</t>
+          <t xml:space="preserve">warm.normal.cool[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここでの経験は、忘れない</t>
+          <t xml:space="preserve">…昨日と同じ動きだ。…なのに、入りが浅い</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.normal.cool[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4450,29 +4450,29 @@
       </c>
       <c r="C129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">cap_reached.normal.cool[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そうか。お世話になった</t>
+          <t xml:space="preserve">……ここが、天井か</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.cool[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.normal.cool[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4482,29 +4482,29 @@
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">ovr_elite.normal.cool[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここでの経験は、忘れない</t>
+          <t xml:space="preserve">……一つの壁を、越えた</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.cool[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.normal.cool[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4514,29 +4514,29 @@
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.normal.cool[1]</t>
+          <t xml:space="preserve">ovr_growth.normal.cool[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…相容れない</t>
+          <t xml:space="preserve">……手応えは、ある</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.cool[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.normal.cool[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4546,29 +4546,29 @@
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.normal.cool[1]</t>
+          <t xml:space="preserve">ovr_legend.normal.cool[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">距離感が…変わった</t>
+          <t xml:space="preserve">……この先に何があるのか。…見てみたい</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.cool[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.normal.cool[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4578,29 +4578,29 @@
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.normal.cool[1]</t>
+          <t xml:space="preserve">pop_growth.normal.cool[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いいバランスだ。やりやすい</t>
+          <t xml:space="preserve">……認知されてきた、か</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.cool[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.normal.cool[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4610,29 +4610,29 @@
       </c>
       <c r="C134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.normal.cool[1]</t>
+          <t xml:space="preserve">pop_star.normal.cool[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">唯一の、本当の仲間だ</t>
+          <t xml:space="preserve">……背負うものが増えた。…それでいい</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.cool[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.normal.cool[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4642,29 +4642,29 @@
       </c>
       <c r="C135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.normal.cool[1]</t>
+          <t xml:space="preserve">normal.cool[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…執着は、消えたか</t>
+          <t xml:space="preserve">……何のために戦っているのか、見えなくなった</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.cool[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.normal.cool[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4674,29 +4674,29 @@
       </c>
       <c r="C136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.normal.cool[1]</t>
+          <t xml:space="preserve">normal.cool[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この存在が…引っかかる</t>
+          <t xml:space="preserve">……思い出した。戦う理由を</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.cool[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.normal.cool[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4706,29 +4706,29 @@
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.normal.cool[1]</t>
+          <t xml:space="preserve">normal.cool[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">倒すまで、止まれない</t>
+          <t xml:space="preserve">……戻ってきた。この感覚だ</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.cool[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.normal.cool[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4738,29 +4738,29 @@
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.normal.cool[1]</t>
+          <t xml:space="preserve">defeat.normal.cool[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着をつけるまで、死んでも死にきれない</t>
+          <t xml:space="preserve">……最近、噛み合わない</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.cool[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.normal.cool[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4770,29 +4770,29 @@
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.normal.cool[1]</t>
+          <t xml:space="preserve">mediaAward.normal.cool[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここが…自分の場所だ</t>
+          <t xml:space="preserve">…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.cool[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.cool[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4802,29 +4802,29 @@
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.normal.cool[1]</t>
+          <t xml:space="preserve">normal.cool[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここにいる理由が…もうない</t>
+          <t xml:space="preserve">ドーム…ね。来たか</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.cool[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.cool[2]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4834,29 +4834,29 @@
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.normal.cool[1]</t>
+          <t xml:space="preserve">normal.cool[2]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この環境に…疑問を感じ始めている</t>
+          <t xml:space="preserve">…やることは、変わらない</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.normal.cool[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.cool[3]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4866,29 +4866,29 @@
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.normal.cool[1]</t>
+          <t xml:space="preserve">normal.cool[3]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負けた。だが、後悔はない</t>
+          <t xml:space="preserve">…準備はできてる</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.normal.cool[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.cool[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4898,29 +4898,29 @@
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.normal.cool[1]</t>
+          <t xml:space="preserve">normal.cool[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……完璧だった</t>
+          <t xml:space="preserve">…満員</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.normal.cool[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.cool[2]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4930,29 +4930,29 @@
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.normal.cool[1]</t>
+          <t xml:space="preserve">normal.cool[2]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……足りないか</t>
+          <t xml:space="preserve">…客の声が、まだ耳に残ってる</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.normal.cool[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.cool[3]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4962,29 +4962,29 @@
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.normal.cool[1]</t>
+          <t xml:space="preserve">normal.cool[3]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った。それでいい</t>
+          <t xml:space="preserve">…忘れない。この景色は</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.normal.cool[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.normal.cool[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4994,29 +4994,29 @@
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.normal.cool[1]</t>
+          <t xml:space="preserve">bonus_insult.normal.cool[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……集中。あと一セット</t>
+          <t xml:space="preserve">……そう。わかった</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.normal.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.normal.cool[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5026,29 +5026,29 @@
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.normal.cool[1]</t>
+          <t xml:space="preserve">E1.normal.cool[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この状況は、よくない</t>
+          <t xml:space="preserve">…メディアの話が来ている。出たい</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.normal.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.normal.cool[2]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5058,29 +5058,29 @@
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.normal.cool[1]</t>
+          <t xml:space="preserve">E1.normal.cool[2]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この環境は、悪くない</t>
+          <t xml:space="preserve">…出演の話。やらせてくれ</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.normal.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.normal.cool[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5090,29 +5090,29 @@
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.normal.cool[1]</t>
+          <t xml:space="preserve">E4.normal.cool[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…おかげで、ここにいる意味がある</t>
+          <t xml:space="preserve">…スカウトの報告が来ている</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.normal.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.normal.cool[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5122,29 +5122,29 @@
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.normal.cool[1]</t>
+          <t xml:space="preserve">E6.normal.cool[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……情報は、自然と入ってくる</t>
+          <t xml:space="preserve">…他団体からオファーが来ている</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.normal.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.normal.cool[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5154,29 +5154,29 @@
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.normal.cool[1]</t>
+          <t xml:space="preserve">S_boycott.normal.cool[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……出番がないのは、つらい</t>
+          <t xml:space="preserve">…………（荷物をまとめて帰ろうとしている）</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.normal.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.normal.cool[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5186,29 +5186,29 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.normal.cool[1]</t>
+          <t xml:space="preserve">S_grumble.normal.cool[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……体が鈍い。これは…まずいな</t>
+          <t xml:space="preserve">（無言で佇んでいるが、周囲が気を遣って重い空気になっている）</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.normal.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.normal.cool[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5218,29 +5218,29 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.normal.cool[1]</t>
+          <t xml:space="preserve">S_sns.normal.cool[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝てない。何が足りない</t>
+          <t xml:space="preserve">（SNSに風景写真と「遠くへ」とだけ投稿。ファンがざわついている）</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.normal.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.normal.cool[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5250,29 +5250,29 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.normal.cool[1]</t>
+          <t xml:space="preserve">S1.normal.cool[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負ける気がしない</t>
+          <t xml:space="preserve">…タイトル戦を。組んでほしい</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.normal.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.normal.cool[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5282,29 +5282,29 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.normal.cool[1]</t>
+          <t xml:space="preserve">S2.normal.cool[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……じっとしているのが、一番つらい</t>
+          <t xml:space="preserve">…あの人との試合を組んでほしい</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.normal.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.normal.cool[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5314,29 +5314,29 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.normal.cool[1]</t>
+          <t xml:space="preserve">S3.normal.cool[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……認識の外。それだけ</t>
+          <t xml:space="preserve">…少し、休みたい</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.normal.cool[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5346,29 +5346,29 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">S4_direct.normal.cool[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">調子は戻った。だが…確実に何かを掴んだ</t>
+          <t xml:space="preserve">…このままでは続けられない。考えてほしい</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.normal.cool[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5378,29 +5378,29 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.cool[1]</t>
+          <t xml:space="preserve">S4_silent.normal.cool[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…身体の感覚は薄い。それでも、立てる。十分</t>
+          <t xml:space="preserve">………（首を振って、口をつぐんだ）</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.cool[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.normal.cool[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5410,29 +5410,29 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.cool[2]</t>
+          <t xml:space="preserve">S5.normal.cool[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最後の一戦。ここまで来た。降りない</t>
+          <t xml:space="preserve">…特訓の時間を。もらえるか</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.normal.cool[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5442,29 +5442,29 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.cool[1]</t>
+          <t xml:space="preserve">S6.normal.cool[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…相手は誰でもいい</t>
+          <t xml:space="preserve">…後輩の指導を。任せてくれ</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.normal.cool[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5474,29 +5474,29 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.cool[2]</t>
+          <t xml:space="preserve">normal.cool[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">真っ向から受ける。それだけ</t>
+          <t xml:space="preserve">…よろしく。精一杯やる</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.normal.cool[2]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5506,29 +5506,29 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.normal.cool[1]</t>
+          <t xml:space="preserve">normal.cool[2]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一人、落とした。息は上がってる。だが、退かない。次</t>
+          <t xml:space="preserve">…選んでくれるなら、全力で応える</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.cool[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5538,29 +5538,29 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.normal.cool[2]</t>
+          <t xml:space="preserve">normal.cool[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ立ってる。それで十分。次を出せ</t>
+          <t xml:space="preserve">……よろしく</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.cool[2]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5570,29 +5570,29 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.cool[1]</t>
+          <t xml:space="preserve">normal.cool[2]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人の勝利。それ以上でも以下でもない</t>
+          <t xml:space="preserve">……全力でやる</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.normal.cool[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5602,29 +5602,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.cool[2]</t>
+          <t xml:space="preserve">normal.cool[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人では成し得なかった。事実としてそう言える</t>
+          <t xml:space="preserve">…よろしく。力になる</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.normal.cool[2]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5634,29 +5634,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.normal.cool[1]</t>
+          <t xml:space="preserve">normal.cool[2]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">個人賞は事実として受け取る。だが、団体は負けた。次がある</t>
+          <t xml:space="preserve">…新しい環境か。悪くない。やる</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.normal.cool[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5666,29 +5666,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.normal.cool[2]</t>
+          <t xml:space="preserve">normal.cool[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足りなかった。それだけ。次で取り返す</t>
+          <t xml:space="preserve">…よろしく。やる</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.normal.cool[2]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5698,29 +5698,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.normal.cool[1]</t>
+          <t xml:space="preserve">normal.cool[2]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体の感覚はとっくに消えてる。それでも足だけは動いた。理由は知らない</t>
+          <t xml:space="preserve">…力になれるよう、精一杯やる</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.normal.cool[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5730,29 +5730,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.normal.cool[2]</t>
+          <t xml:space="preserve">normal.cool[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人抜いたかより、最後に立っていたことだけが事実</t>
+          <t xml:space="preserve">……すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.normal.cool[2]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5762,29 +5762,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.cool[1]</t>
+          <t xml:space="preserve">normal.cool[2]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……優勝。……次のステージへ</t>
+          <t xml:space="preserve">……心配はいらない</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.normal.cool[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5794,29 +5794,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.cool[2]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.normal.cool[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとう</t>
+          <t xml:space="preserve">……済んだ話だ。まだ気にする方がどうかしてる</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.normal.cool[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5826,29 +5826,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.normal.cool[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.normal.cool[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ足りない</t>
+          <t xml:space="preserve">……決着はついた。納得したとは、言ってない</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.normal.cool[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5858,29 +5858,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.normal.cool[2]</t>
+          <t xml:space="preserve">draftInterest.normal.cool[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は負けない</t>
+          <t xml:space="preserve">…よろしく。精一杯やる</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.normal.cool[2]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5890,29 +5890,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.normal.cool[1]</t>
+          <t xml:space="preserve">draftInterest.normal.cool[2]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一勝。次</t>
+          <t xml:space="preserve">…選んでくれるなら、全力で応える</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.cool[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5922,29 +5922,29 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.normal.cool[2]</t>
+          <t xml:space="preserve">draftJoin.normal.cool[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだだ</t>
+          <t xml:space="preserve">……よろしく</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.cool[2]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5954,29 +5954,29 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.normal.cool[1]</t>
+          <t xml:space="preserve">draftJoin.normal.cool[2]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悪くなかった</t>
+          <t xml:space="preserve">……全力でやる</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.normal.cool[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5986,29 +5986,29 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.normal.cool[2]</t>
+          <t xml:space="preserve">faGreeting.normal.cool[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……収穫はあった</t>
+          <t xml:space="preserve">…契約は契約。きっちり働く</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.normal.cool[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6018,29 +6018,29 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.cool[1]</t>
+          <t xml:space="preserve">faSigning.normal.cool[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……決勝。全て出す</t>
+          <t xml:space="preserve">…よろしく。力になる</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.normal.cool[2]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6050,29 +6050,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.cool[2]</t>
+          <t xml:space="preserve">faSigning.normal.cool[2]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……最後の一戦</t>
+          <t xml:space="preserve">…新しい環境か。悪くない。やる</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.normal.cool[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6082,29 +6082,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.cool[1]</t>
+          <t xml:space="preserve">faWelcome.normal.cool[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……集中する</t>
+          <t xml:space="preserve">…よろしく。やる</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.normal.cool[2]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6114,29 +6114,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.cool[2]</t>
+          <t xml:space="preserve">faWelcome.normal.cool[2]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……行く</t>
+          <t xml:space="preserve">…力になれるよう、精一杯やる</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.normal.cool[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6146,29 +6146,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.normal.cool[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.normal.cool[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……出る。それだけだ</t>
+          <t xml:space="preserve">…調子はいい。今なら、何をやっても身につく</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.normal.cool[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6178,29 +6178,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.normal.cool[2]</t>
+          <t xml:space="preserve">heatSelf.heavy.normal.cool[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝つだけだ</t>
+          <t xml:space="preserve">…体が重い。今日は、何をやっても素通りだ</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.normal.cool[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6210,29 +6210,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">heatSelf.warm.normal.cool[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……受けて立つ。全力だ</t>
+          <t xml:space="preserve">…昨日と同じ動きだ。…なのに、入りが浅い</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.cool[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6242,29 +6242,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">injury.normal.cool[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここが頂点。……でも、まだ先がある</t>
+          <t xml:space="preserve">……すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.cool[2]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6274,29 +6274,29 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">injury.normal.cool[2]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った。（静かにベルトを掲げる）</t>
+          <t xml:space="preserve">……心配はいらない</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.cool[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6306,29 +6306,29 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">release.normal.cool[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……挑戦する。受けろ</t>
+          <t xml:space="preserve">……そうか。お世話になった</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.cool[2]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6338,29 +6338,29 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">release.normal.cool[2]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……実力で語る。それだけだ</t>
+          <t xml:space="preserve">……ここでの経験は、忘れない</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.normal.cool[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6370,29 +6370,29 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">rentalGreeting.normal.cool[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……臆病者</t>
+          <t xml:space="preserve">…レンタルだが、手は抜かない。よろしく</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.normal.cool[2]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6402,29 +6402,29 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">rentalGreeting.normal.cool[2]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……逃げたか</t>
+          <t xml:space="preserve">…短い間だ。よろしく</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.normal.cool[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6434,29 +6434,29 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.normal.cool[1]</t>
+          <t xml:space="preserve">scoutGreeting.normal.cool[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負けた。……受け止める</t>
+          <t xml:space="preserve">…話は受けた。あとは試合で</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.normal.cool[2]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6466,29 +6466,29 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.normal.cool[2]</t>
+          <t xml:space="preserve">scoutGreeting.normal.cool[2]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は違う</t>
+          <t xml:space="preserve">…期待は、悪くない</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.normal.cool[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6498,29 +6498,29 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.normal.cool[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.normal.cool[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った。それが全てだ</t>
+          <t xml:space="preserve">…悔しい。だが、糧にはなった。次だ</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.normal.cool[2]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6530,29 +6530,29 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.normal.cool[2]</t>
+          <t xml:space="preserve">titleChallengeLoss.normal.cool[2]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悪くない</t>
+          <t xml:space="preserve">…実力が足りなかった。強くなって戻る</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.normal.cool[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6562,29 +6562,29 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">titleDefense.normal.cool[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…団体の看板、背負えた</t>
+          <t xml:space="preserve">…防衛。…だが、まだ足りない</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.normal.cool[2]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6594,29 +6594,29 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">titleDefense.normal.cool[2]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝った。それだけ</t>
+          <t xml:space="preserve">…守るたびに、このベルトの重さがわかる</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.normal.cool[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.normal.cool[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6626,59 +6626,2779 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[3]</t>
+          <t xml:space="preserve">titleLoss.normal.cool[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った。それでいい</t>
+          <t xml:space="preserve">…失った。だが、ここで戦い続ける</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleLoss.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…悔しい。チャンピオンとして、もっとやれたはずだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="40" customHeight="1">
+      <c r="A199" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleWin.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…獲った。チャンピオンだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="40" customHeight="1">
+      <c r="A200" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleWin.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…このベルトは手放さない</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="40" customHeight="1">
+      <c r="A201" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……そうか。お世話になった</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="40" customHeight="1">
+      <c r="A202" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ここでの経験は、忘れない</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="40" customHeight="1">
+      <c r="A203" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…レンタルだが、手は抜かない。よろしく</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="40" customHeight="1">
+      <c r="A204" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…短い間だ。よろしく</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="40" customHeight="1">
+      <c r="A205" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…悔しい。だが、糧にはなった。次だ</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="40" customHeight="1">
+      <c r="A206" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…実力が足りなかった。強くなって戻る</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="40" customHeight="1">
+      <c r="A207" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…防衛。…だが、まだ足りない</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="40" customHeight="1">
+      <c r="A208" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…守るたびに、このベルトの重さがわかる</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="40" customHeight="1">
+      <c r="A209" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…失った。だが、ここで戦い続ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="40" customHeight="1">
+      <c r="A210" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…悔しい。チャンピオンとして、もっとやれたはずだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="40" customHeight="1">
+      <c r="A211" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…獲った。チャンピオンだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="40" customHeight="1">
+      <c r="A212" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…このベルトは手放さない</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="40" customHeight="1">
+      <c r="A213" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_39_down.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…相容れない</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="40" customHeight="1">
+      <c r="A214" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_59_down.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">距離感が…変わった</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="40" customHeight="1">
+      <c r="A215" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_60_up.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いいバランスだ。やりやすい</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="40" customHeight="1">
+      <c r="A216" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_80_up.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">唯一の、本当の仲間だ</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="40" customHeight="1">
+      <c r="A217" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_29_down.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…執着は、消えたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="40" customHeight="1">
+      <c r="A218" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_30_up.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この存在が…引っかかる</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="40" customHeight="1">
+      <c r="A219" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_50_up.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">倒すまで、止まれない</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="40" customHeight="1">
+      <c r="A220" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_70_up.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">決着をつけるまで、死んでも死にきれない</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="40" customHeight="1">
+      <c r="A221" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_above_75.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここが…自分の場所だ</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="40" customHeight="1">
+      <c r="A222" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_20.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここにいる理由が…もうない</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="40" customHeight="1">
+      <c r="A223" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_35.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この環境に…疑問を感じ始めている</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="40" customHeight="1">
+      <c r="A224" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-01.goodLoss.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……負けた。だが、後悔はない</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="40" customHeight="1">
+      <c r="A225" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-01.greatWin.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……完璧だった</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="40" customHeight="1">
+      <c r="A226" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-01.loss.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……足りないか</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="40" customHeight="1">
+      <c r="A227" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-01.win.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……勝った。それでいい</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="40" customHeight="1">
+      <c r="A228" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-02.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……集中。あと一セット</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="40" customHeight="1">
+      <c r="A229" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-03.down.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……この状況は、よくない</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="40" customHeight="1">
+      <c r="A230" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-03.up.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……この環境は、悪くない</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="40" customHeight="1">
+      <c r="A231" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-04.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…おかげで、ここにいる意味がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="40" customHeight="1">
+      <c r="A232" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-05.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……情報は、自然と入ってくる</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="40" customHeight="1">
+      <c r="A233" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-06.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……出番がないのは、つらい</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="40" customHeight="1">
+      <c r="A234" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-07.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……体が鈍い。これは…まずいな</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="40" customHeight="1">
+      <c r="A235" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-08.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……勝てない。何が足りない</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="40" customHeight="1">
+      <c r="A236" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-09.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……負ける気がしない</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="40" customHeight="1">
+      <c r="A237" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-10.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……じっとしているのが、一番つらい</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="40" customHeight="1">
+      <c r="A238" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">GL-11.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……認識の外。それだけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="40" customHeight="1">
+      <c r="A239" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">調子は戻った。だが…確実に何かを掴んだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="40" customHeight="1">
+      <c r="A240" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…身体の感覚は薄い。それでも、立てる。十分</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="40" customHeight="1">
+      <c r="A241" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…最後の一戦。ここまで来た。降りない</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="40" customHeight="1">
+      <c r="A242" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…相手は誰でもいい</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="40" customHeight="1">
+      <c r="A243" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">真っ向から受ける。それだけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="40" customHeight="1">
+      <c r="A244" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…一人、落とした。息は上がってる。だが、退かない。次</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="40" customHeight="1">
+      <c r="A245" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…まだ立ってる。それで十分。次を出せ</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="40" customHeight="1">
+      <c r="A246" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">三人の勝利。それ以上でも以下でもない</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="40" customHeight="1">
+      <c r="A247" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一人では成し得なかった。事実としてそう言える</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="40" customHeight="1">
+      <c r="A248" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">個人賞は事実として受け取る。だが、団体は負けた。次がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="40" customHeight="1">
+      <c r="A249" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">足りなかった。それだけ。次で取り返す</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="40" customHeight="1">
+      <c r="A250" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">身体の感覚はとっくに消えてる。それでも足だけは動いた。理由は知らない</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="40" customHeight="1">
+      <c r="A251" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">何人抜いたかより、最後に立っていたことだけが事実</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="40" customHeight="1">
+      <c r="A252" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……優勝。……次のステージへ</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="40" customHeight="1">
+      <c r="A253" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ありがとう</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="40" customHeight="1">
+      <c r="A254" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postLose.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……まだ足りない</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="40" customHeight="1">
+      <c r="A255" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postLose.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……次は負けない</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="40" customHeight="1">
+      <c r="A256" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……一勝。次</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="40" customHeight="1">
+      <c r="A257" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……まだだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="40" customHeight="1">
+      <c r="A258" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postWin.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……悪くなかった</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="40" customHeight="1">
+      <c r="A259" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postWin.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……収穫はあった</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="40" customHeight="1">
+      <c r="A260" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……決勝。全て出す</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="40" customHeight="1">
+      <c r="A261" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……最後の一戦</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="40" customHeight="1">
+      <c r="A262" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……集中する</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="40" customHeight="1">
+      <c r="A263" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……行く</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="40" customHeight="1">
+      <c r="A264" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……出る。それだけだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="40" customHeight="1">
+      <c r="A265" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……勝つだけだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="40" customHeight="1">
+      <c r="A266" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……受けて立つ。全力だ</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="40" customHeight="1">
+      <c r="A267" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ここが頂点。……でも、まだ先がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="40" customHeight="1">
+      <c r="A268" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……勝った。（静かにベルトを掲げる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="40" customHeight="1">
+      <c r="A269" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……挑戦する。受けろ</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="40" customHeight="1">
+      <c r="A270" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……実力で語る。それだけだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="40" customHeight="1">
+      <c r="A271" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……臆病者</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="40" customHeight="1">
+      <c r="A272" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……逃げたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="40" customHeight="1">
+      <c r="A273" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……負けた。……受け止める</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="40" customHeight="1">
+      <c r="A274" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……次は違う</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="40" customHeight="1">
+      <c r="A275" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……勝った。それが全てだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="40" customHeight="1">
+      <c r="A276" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……悪くない</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="40" customHeight="1">
+      <c r="A277" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…団体の看板、背負えた</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="40" customHeight="1">
+      <c r="A278" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…勝った。それだけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="40" customHeight="1">
+      <c r="A279" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.normal.cool[3]</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.cool[3]</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……勝った。それでいい</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="40" customHeight="1">
+      <c r="A280" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">ENDING_LINES.fighter.normal.cool[1]</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr" s="2">
+      <c r="B280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr" s="12">
+      <c r="D280" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighter.normal.cool[1]</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr" s="2">
+      <c r="E280" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr" s="3">
+      <c r="F280" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">……終わったか。……悪くない</t>
         </is>
       </c>
     </row>
+    <row r="281" ht="40" customHeight="1">
+      <c r="A281" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…契約は契約。きっちり働く</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="40" customHeight="1">
+      <c r="A282" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.cool[1]</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…話は受けた。あとは試合で</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="40" customHeight="1">
+      <c r="A283" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.cool[2]</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…期待は、悪くない</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H198"/>
+  <autoFilter ref="A1:H283"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/クール×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/クール×ノーマル.xlsx
@@ -376,7 +376,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.normal.cool[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.cool.normal[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -391,7 +391,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.normal.cool[1]</t>
+          <t xml:space="preserve">atk.cool.normal[1]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -408,7 +408,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.normal.cool[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.cool.normal[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -423,7 +423,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.normal.cool[2]</t>
+          <t xml:space="preserve">atk.cool.normal[2]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -440,7 +440,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.normal.cool[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.cool.normal[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -455,7 +455,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.normal.cool[3]</t>
+          <t xml:space="preserve">atk.cool.normal[3]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -472,7 +472,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.normal.cool[4]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.cool.normal[4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -487,7 +487,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.normal.cool[4]</t>
+          <t xml:space="preserve">atk.cool.normal[4]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -504,7 +504,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.normal.cool[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.cool.normal[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -519,7 +519,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.normal.cool[1]</t>
+          <t xml:space="preserve">bigmove.cool.normal[1]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
@@ -536,7 +536,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.normal.cool[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.cool.normal[2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -551,7 +551,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.normal.cool[2]</t>
+          <t xml:space="preserve">bigmove.cool.normal[2]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
@@ -568,7 +568,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.normal.cool[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.cool.normal[3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -583,7 +583,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.normal.cool[3]</t>
+          <t xml:space="preserve">bigmove.cool.normal[3]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
@@ -600,7 +600,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.normal.cool[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.cool.normal[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -615,7 +615,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.normal.cool[1]</t>
+          <t xml:space="preserve">climax.cool.normal[1]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
@@ -632,7 +632,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.normal.cool[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.cool.normal[2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -647,7 +647,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.normal.cool[2]</t>
+          <t xml:space="preserve">climax.cool.normal[2]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
@@ -664,7 +664,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -679,7 +679,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
@@ -696,7 +696,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.normal.cool[2]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -711,7 +711,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
@@ -728,7 +728,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.normal.cool[3]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.cool.normal[3]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -743,7 +743,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[3]</t>
+          <t xml:space="preserve">cool.normal[3]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
@@ -760,7 +760,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.normal.cool[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.cool.normal[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -775,7 +775,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.normal.cool[1]</t>
+          <t xml:space="preserve">badWinner.cool.normal[1]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
@@ -792,7 +792,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.normal.cool[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.cool.normal[1]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -807,7 +807,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.normal.cool[1]</t>
+          <t xml:space="preserve">goodWinner.cool.normal[1]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
@@ -824,7 +824,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.normal.cool[2]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.cool.normal[2]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -839,7 +839,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.normal.cool[2]</t>
+          <t xml:space="preserve">goodWinner.cool.normal[2]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
@@ -856,7 +856,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.normal.cool[2]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -871,7 +871,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
@@ -888,7 +888,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.normal.cool[2]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.cool.normal[2]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -903,7 +903,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal.cool[2]</t>
+          <t xml:space="preserve">loser.cool.normal[2]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
@@ -920,7 +920,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.normal.cool[2]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.cool.normal[2]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -935,7 +935,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.cool[2]</t>
+          <t xml:space="preserve">winner.cool.normal[2]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
@@ -952,7 +952,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.normal.cool[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.cool.normal[1]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -967,7 +967,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.normal.cool[1]</t>
+          <t xml:space="preserve">competition_won.cool.normal[1]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
@@ -984,7 +984,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.normal.cool[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.cool.normal[1]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -999,7 +999,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.normal.cool[1]</t>
+          <t xml:space="preserve">direct.cool.normal[1]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
@@ -1016,7 +1016,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.normal.cool[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.cool.normal[1]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.normal.cool[1]</t>
+          <t xml:space="preserve">fa_signing.cool.normal[1]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
@@ -1048,7 +1048,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.normal.cool.hit[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.cool.normal.hit[1]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool.hit[1]</t>
+          <t xml:space="preserve">cool.normal.hit[1]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
@@ -1080,7 +1080,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.normal.cool.hit[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.cool.normal.hit[2]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool.hit[2]</t>
+          <t xml:space="preserve">cool.normal.hit[2]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
@@ -1112,7 +1112,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.normal.cool.win[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.cool.normal.win[1]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool.win[1]</t>
+          <t xml:space="preserve">cool.normal.win[1]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
@@ -1144,7 +1144,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.normal.cool.win[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.cool.normal.win[2]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool.win[2]</t>
+          <t xml:space="preserve">cool.normal.win[2]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
@@ -1176,7 +1176,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.normal.cool[2]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
@@ -1208,7 +1208,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.normal.cool[3]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.cool.normal[3]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[3]</t>
+          <t xml:space="preserve">cool.normal[3]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
@@ -1240,7 +1240,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
@@ -1272,7 +1272,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.normal.cool[2]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
@@ -1304,7 +1304,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.normal.cool[3]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.cool.normal[3]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[3]</t>
+          <t xml:space="preserve">cool.normal[3]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
@@ -1336,7 +1336,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
@@ -1368,7 +1368,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.normal.cool[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
@@ -1400,7 +1400,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.normal.cool[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.cool.normal[3]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[3]</t>
+          <t xml:space="preserve">cool.normal[3]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="2">
@@ -1432,7 +1432,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="2">
@@ -1464,7 +1464,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.normal.cool[2]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
@@ -1496,7 +1496,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.normal.cool[3]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.cool.normal[3]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[3]</t>
+          <t xml:space="preserve">cool.normal[3]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
@@ -1528,7 +1528,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
@@ -1560,7 +1560,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.normal.cool[2]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr" s="2">
@@ -1592,7 +1592,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
@@ -1624,7 +1624,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.normal.cool[2]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
@@ -1656,7 +1656,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.normal.cool[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.cool.normal[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ahead.normal.cool[1]</t>
+          <t xml:space="preserve">ahead.cool.normal[1]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
@@ -1688,7 +1688,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.normal.cool[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.cool.normal[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">behind.normal.cool[1]</t>
+          <t xml:space="preserve">behind.cool.normal[1]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
@@ -1720,7 +1720,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.normal.cool[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.cool.normal[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal.cool[1]</t>
+          <t xml:space="preserve">loser.cool.normal[1]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
@@ -1752,7 +1752,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.normal.cool[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.cool.normal[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.cool[1]</t>
+          <t xml:space="preserve">winner.cool.normal[1]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="2">
@@ -1784,7 +1784,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.normal.cool[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.cool.normal[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.cool[1]</t>
+          <t xml:space="preserve">winner.cool.normal[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1816,7 +1816,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.normal.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.cool.normal[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal.cool[1]</t>
+          <t xml:space="preserve">attacker.cool.normal[1]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -1848,7 +1848,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.normal.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.cool.normal[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal.cool[1]</t>
+          <t xml:space="preserve">defender.cool.normal[1]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -1880,7 +1880,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.normal.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.cool.normal[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal.cool[1]</t>
+          <t xml:space="preserve">attacker.cool.normal[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -1912,7 +1912,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.normal.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.cool.normal[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal.cool[1]</t>
+          <t xml:space="preserve">defender.cool.normal[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -1944,7 +1944,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.normal.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.cool.normal[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal.cool[1]</t>
+          <t xml:space="preserve">attacker.cool.normal[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -1976,7 +1976,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.normal.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.cool.normal[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal.cool[1]</t>
+          <t xml:space="preserve">defender.cool.normal[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -2008,7 +2008,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.normal.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.cool.normal[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.normal.cool[1]</t>
+          <t xml:space="preserve">fateAttacker.cool.normal[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -2040,7 +2040,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.normal.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.cool.normal[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.normal.cool[1]</t>
+          <t xml:space="preserve">fateDefender.cool.normal[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2072,7 +2072,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.normal.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.cool.normal[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.normal.cool[1]</t>
+          <t xml:space="preserve">loserLines.cool.normal[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2104,7 +2104,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.normal.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.cool.normal[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.normal.cool[1]</t>
+          <t xml:space="preserve">winnerLines.cool.normal[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2136,7 +2136,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.normal.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.cool.normal[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.normal.cool[1]</t>
+          <t xml:space="preserve">fateLoser.cool.normal[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2168,7 +2168,7 @@
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.normal.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.cool.normal[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.normal.cool[1]</t>
+          <t xml:space="preserve">fateWinner.cool.normal[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -2200,7 +2200,7 @@
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.normal.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.cool.normal[1]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal.cool[1]</t>
+          <t xml:space="preserve">loser.cool.normal[1]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
@@ -2232,7 +2232,7 @@
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.normal.cool[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.cool.normal[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.cool[1]</t>
+          <t xml:space="preserve">winner.cool.normal[1]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
@@ -2264,7 +2264,7 @@
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.normal.cool[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.cool.normal[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.normal.cool[1]</t>
+          <t xml:space="preserve">loserLines.cool.normal[1]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
@@ -2296,7 +2296,7 @@
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.normal.cool[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.cool.normal[1]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.normal.cool[1]</t>
+          <t xml:space="preserve">winnerLines.cool.normal[1]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr" s="2">
@@ -2328,7 +2328,7 @@
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.normal.cool[1]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.cool.normal[1]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.normal.cool[1]</t>
+          <t xml:space="preserve">awakening.cool.normal[1]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr" s="2">
@@ -3128,7 +3128,7 @@
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.normal.cool[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.cool.normal[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.normal.cool[1]</t>
+          <t xml:space="preserve">accepted.cool.normal[1]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3160,7 +3160,7 @@
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.normal.cool[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.cool.normal[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.normal.cool[1]</t>
+          <t xml:space="preserve">defended.cool.normal[1]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3192,7 +3192,7 @@
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.normal.cool[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.cool.normal[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.normal.cool[1]</t>
+          <t xml:space="preserve">defense_failed.cool.normal[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3224,7 +3224,7 @@
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.normal.cool[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.cool.normal[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.normal.cool[1]</t>
+          <t xml:space="preserve">former_champ.cool.normal[1]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3256,7 +3256,7 @@
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.normal.cool[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.cool.normal[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.normal.cool[1]</t>
+          <t xml:space="preserve">accept_terminal.cool.normal[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3288,7 +3288,7 @@
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.normal.cool[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.cool.normal[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.normal.cool[1]</t>
+          <t xml:space="preserve">refuse_champ.cool.normal[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3320,7 +3320,7 @@
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.normal.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.cool.normal[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.normal.cool[1]</t>
+          <t xml:space="preserve">A1_champion.cool.normal[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3352,7 +3352,7 @@
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.normal.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.cool.normal[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.normal.cool[1]</t>
+          <t xml:space="preserve">A2_uncrowned.cool.normal[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3384,7 +3384,7 @@
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.normal.cool[2]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.cool.normal[2]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.normal.cool[2]</t>
+          <t xml:space="preserve">A2_uncrowned.cool.normal[2]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3416,7 +3416,7 @@
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.normal.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.cool.normal[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.normal.cool[1]</t>
+          <t xml:space="preserve">A3_heel.cool.normal[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3448,7 +3448,7 @@
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.normal.cool[2]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.cool.normal[2]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.normal.cool[2]</t>
+          <t xml:space="preserve">A3_heel.cool.normal[2]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3480,7 +3480,7 @@
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.normal.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.cool.normal[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.normal.cool[1]</t>
+          <t xml:space="preserve">A4_veteran.cool.normal[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3512,7 +3512,7 @@
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.normal.cool[2]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.cool.normal[2]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.normal.cool[2]</t>
+          <t xml:space="preserve">A4_veteran.cool.normal[2]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3544,7 +3544,7 @@
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.normal.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.cool.normal[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.normal.cool[1]</t>
+          <t xml:space="preserve">B1_young.cool.normal[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3576,7 +3576,7 @@
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.normal.cool[2]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.cool.normal[2]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.normal.cool[2]</t>
+          <t xml:space="preserve">B1_young.cool.normal[2]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3608,7 +3608,7 @@
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.normal.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.cool.normal[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.normal.cool[1]</t>
+          <t xml:space="preserve">B2_prime.cool.normal[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3640,7 +3640,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.normal.cool[2]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.cool.normal[2]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.normal.cool[2]</t>
+          <t xml:space="preserve">B2_prime.cool.normal[2]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3672,7 +3672,7 @@
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.normal.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.cool.normal[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.normal.cool[1]</t>
+          <t xml:space="preserve">B3_older.cool.normal[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3704,7 +3704,7 @@
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.normal.cool[2]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.cool.normal[2]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.normal.cool[2]</t>
+          <t xml:space="preserve">B3_older.cool.normal[2]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3736,7 +3736,7 @@
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.normal.cool[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.cool.normal[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.normal.cool[1]</t>
+          <t xml:space="preserve">B4_champion_injury.cool.normal[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3768,7 +3768,7 @@
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.normal.cool[2]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.cool.normal[2]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.normal.cool[2]</t>
+          <t xml:space="preserve">B4_champion_injury.cool.normal[2]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3800,7 +3800,7 @@
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3832,7 +3832,7 @@
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.normal.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.cool.normal[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.normal.cool[1]</t>
+          <t xml:space="preserve">raise_accept.cool.normal[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3864,7 +3864,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.normal.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.cool.normal[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.normal.cool[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.cool.normal[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3896,7 +3896,7 @@
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.normal.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.cool.normal[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.normal.cool[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.cool.normal[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3928,7 +3928,7 @@
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.normal.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.cool.normal[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.normal.cool[1]</t>
+          <t xml:space="preserve">raise_open.cool.normal[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3960,7 +3960,7 @@
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.normal.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.cool.normal[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.normal.cool[1]</t>
+          <t xml:space="preserve">raise_refuse.cool.normal[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3992,7 +3992,7 @@
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.normal.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.cool.normal[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.normal.cool[1]</t>
+          <t xml:space="preserve">sudden_departure.cool.normal[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -4024,7 +4024,7 @@
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.normal.cool[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.cool.normal[2]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.normal.cool[2]</t>
+          <t xml:space="preserve">sudden_departure.cool.normal[2]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4056,7 +4056,7 @@
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.normal.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.cool.normal[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.normal.cool[1]</t>
+          <t xml:space="preserve">transfer_listen.cool.normal[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4088,7 +4088,7 @@
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.normal.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.cool.normal[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.normal.cool[1]</t>
+          <t xml:space="preserve">transfer_open.cool.normal[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4120,7 +4120,7 @@
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.normal.cool[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.cool.normal[2]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.normal.cool[2]</t>
+          <t xml:space="preserve">transfer_open.cool.normal[2]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4152,7 +4152,7 @@
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.normal.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.cool.normal[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.normal.cool[1]</t>
+          <t xml:space="preserve">transfer_release.cool.normal[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4184,7 +4184,7 @@
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.normal.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.cool.normal[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.normal.cool[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.cool.normal[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4216,7 +4216,7 @@
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.normal.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.cool.normal[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.normal.cool[1]</t>
+          <t xml:space="preserve">transfer_retain_success.cool.normal[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4248,7 +4248,7 @@
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.normal.cool[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.cool.normal[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.normal.cool[1]</t>
+          <t xml:space="preserve">start.cool.normal[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4280,7 +4280,7 @@
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4312,7 +4312,7 @@
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4344,7 +4344,7 @@
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.normal.cool[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.cool.normal[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh.normal.cool[1]</t>
+          <t xml:space="preserve">fresh.cool.normal[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -4376,7 +4376,7 @@
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.normal.cool[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.cool.normal[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy.normal.cool[1]</t>
+          <t xml:space="preserve">heavy.cool.normal[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -4408,7 +4408,7 @@
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.normal.cool[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.cool.normal[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm.normal.cool[1]</t>
+          <t xml:space="preserve">warm.cool.normal[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -4440,7 +4440,7 @@
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.normal.cool[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.cool.normal[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.normal.cool[1]</t>
+          <t xml:space="preserve">cap_reached.cool.normal[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4472,7 +4472,7 @@
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.normal.cool[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.cool.normal[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.normal.cool[1]</t>
+          <t xml:space="preserve">ovr_elite.cool.normal[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4504,7 +4504,7 @@
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.normal.cool[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.cool.normal[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.normal.cool[1]</t>
+          <t xml:space="preserve">ovr_growth.cool.normal[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4536,7 +4536,7 @@
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.normal.cool[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.cool.normal[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.normal.cool[1]</t>
+          <t xml:space="preserve">ovr_legend.cool.normal[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4568,7 +4568,7 @@
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.normal.cool[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.cool.normal[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.normal.cool[1]</t>
+          <t xml:space="preserve">pop_growth.cool.normal[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4600,7 +4600,7 @@
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.normal.cool[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.cool.normal[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.normal.cool[1]</t>
+          <t xml:space="preserve">pop_star.cool.normal[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4632,7 +4632,7 @@
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4664,7 +4664,7 @@
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4696,7 +4696,7 @@
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4728,7 +4728,7 @@
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.normal.cool[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.cool.normal[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.normal.cool[1]</t>
+          <t xml:space="preserve">defeat.cool.normal[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4760,7 +4760,7 @@
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.normal.cool[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.cool.normal[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.normal.cool[1]</t>
+          <t xml:space="preserve">mediaAward.cool.normal[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4792,7 +4792,7 @@
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4824,7 +4824,7 @@
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.cool[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4856,7 +4856,7 @@
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.cool[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.cool.normal[3]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[3]</t>
+          <t xml:space="preserve">cool.normal[3]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4888,7 +4888,7 @@
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4920,7 +4920,7 @@
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.cool[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4952,7 +4952,7 @@
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.cool[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.cool.normal[3]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[3]</t>
+          <t xml:space="preserve">cool.normal[3]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4984,7 +4984,7 @@
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.normal.cool[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.cool.normal[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.normal.cool[1]</t>
+          <t xml:space="preserve">bonus_insult.cool.normal[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -5016,7 +5016,7 @@
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.normal.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.cool.normal[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.normal.cool[1]</t>
+          <t xml:space="preserve">E1.cool.normal[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5048,7 +5048,7 @@
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.normal.cool[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.cool.normal[2]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.normal.cool[2]</t>
+          <t xml:space="preserve">E1.cool.normal[2]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5080,7 +5080,7 @@
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.normal.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.cool.normal[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E4.normal.cool[1]</t>
+          <t xml:space="preserve">E4.cool.normal[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5112,7 +5112,7 @@
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.normal.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.cool.normal[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.normal.cool[1]</t>
+          <t xml:space="preserve">E6.cool.normal[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5144,7 +5144,7 @@
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.normal.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.cool.normal[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.normal.cool[1]</t>
+          <t xml:space="preserve">S_boycott.cool.normal[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5176,7 +5176,7 @@
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.normal.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.cool.normal[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.normal.cool[1]</t>
+          <t xml:space="preserve">S_grumble.cool.normal[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5208,7 +5208,7 @@
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.normal.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.cool.normal[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.normal.cool[1]</t>
+          <t xml:space="preserve">S_sns.cool.normal[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5240,7 +5240,7 @@
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.normal.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.cool.normal[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.normal.cool[1]</t>
+          <t xml:space="preserve">S1.cool.normal[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5272,7 +5272,7 @@
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.normal.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.cool.normal[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.normal.cool[1]</t>
+          <t xml:space="preserve">S2.cool.normal[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5304,7 +5304,7 @@
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.normal.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.cool.normal[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.normal.cool[1]</t>
+          <t xml:space="preserve">S3.cool.normal[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5336,7 +5336,7 @@
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.normal.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.cool.normal[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.normal.cool[1]</t>
+          <t xml:space="preserve">S4_direct.cool.normal[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5368,7 +5368,7 @@
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.normal.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.cool.normal[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.normal.cool[1]</t>
+          <t xml:space="preserve">S4_silent.cool.normal[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5400,7 +5400,7 @@
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.normal.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.cool.normal[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.normal.cool[1]</t>
+          <t xml:space="preserve">S5.cool.normal[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5432,7 +5432,7 @@
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.normal.cool[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.cool.normal[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.normal.cool[1]</t>
+          <t xml:space="preserve">S6.cool.normal[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5464,7 +5464,7 @@
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5496,7 +5496,7 @@
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5528,7 +5528,7 @@
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5560,7 +5560,7 @@
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5592,7 +5592,7 @@
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5624,7 +5624,7 @@
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5656,7 +5656,7 @@
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5688,7 +5688,7 @@
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5720,7 +5720,7 @@
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5752,7 +5752,7 @@
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5784,7 +5784,7 @@
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.cool.normal[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.normal.cool[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.cool.normal[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5816,7 +5816,7 @@
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.cool.normal[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.normal.cool[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.cool.normal[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5848,7 +5848,7 @@
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.cool.normal[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.normal.cool[1]</t>
+          <t xml:space="preserve">draftInterest.cool.normal[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5880,7 +5880,7 @@
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.cool.normal[2]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.normal.cool[2]</t>
+          <t xml:space="preserve">draftInterest.cool.normal[2]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5912,7 +5912,7 @@
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.cool.normal[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.normal.cool[1]</t>
+          <t xml:space="preserve">draftJoin.cool.normal[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5944,7 +5944,7 @@
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.cool.normal[2]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.normal.cool[2]</t>
+          <t xml:space="preserve">draftJoin.cool.normal[2]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5976,7 +5976,7 @@
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.cool.normal[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.normal.cool[1]</t>
+          <t xml:space="preserve">faGreeting.cool.normal[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -6008,7 +6008,7 @@
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.cool.normal[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.normal.cool[1]</t>
+          <t xml:space="preserve">faSigning.cool.normal[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6040,7 +6040,7 @@
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.cool.normal[2]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.normal.cool[2]</t>
+          <t xml:space="preserve">faSigning.cool.normal[2]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6072,7 +6072,7 @@
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.cool.normal[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.normal.cool[1]</t>
+          <t xml:space="preserve">faWelcome.cool.normal[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6104,7 +6104,7 @@
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.cool.normal[2]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.normal.cool[2]</t>
+          <t xml:space="preserve">faWelcome.cool.normal[2]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6136,7 +6136,7 @@
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.cool.normal[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.normal.cool[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.cool.normal[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6168,7 +6168,7 @@
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.cool.normal[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.normal.cool[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.cool.normal[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6200,7 +6200,7 @@
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.cool.normal[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.normal.cool[1]</t>
+          <t xml:space="preserve">heatSelf.warm.cool.normal[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6232,7 +6232,7 @@
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.cool.normal[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.normal.cool[1]</t>
+          <t xml:space="preserve">injury.cool.normal[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6264,7 +6264,7 @@
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.cool.normal[2]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.normal.cool[2]</t>
+          <t xml:space="preserve">injury.cool.normal[2]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6296,7 +6296,7 @@
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.cool.normal[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.normal.cool[1]</t>
+          <t xml:space="preserve">release.cool.normal[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6328,7 +6328,7 @@
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.cool.normal[2]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.normal.cool[2]</t>
+          <t xml:space="preserve">release.cool.normal[2]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6360,7 +6360,7 @@
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.cool.normal[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.normal.cool[1]</t>
+          <t xml:space="preserve">rentalGreeting.cool.normal[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6392,7 +6392,7 @@
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.cool.normal[2]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.normal.cool[2]</t>
+          <t xml:space="preserve">rentalGreeting.cool.normal[2]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6424,7 +6424,7 @@
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.cool.normal[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.normal.cool[1]</t>
+          <t xml:space="preserve">scoutGreeting.cool.normal[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6456,7 +6456,7 @@
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.cool.normal[2]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.normal.cool[2]</t>
+          <t xml:space="preserve">scoutGreeting.cool.normal[2]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6488,7 +6488,7 @@
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.cool.normal[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.normal.cool[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.cool.normal[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6520,7 +6520,7 @@
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.cool.normal[2]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.normal.cool[2]</t>
+          <t xml:space="preserve">titleChallengeLoss.cool.normal[2]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6552,7 +6552,7 @@
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.cool.normal[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.normal.cool[1]</t>
+          <t xml:space="preserve">titleDefense.cool.normal[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6584,7 +6584,7 @@
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.cool.normal[2]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.normal.cool[2]</t>
+          <t xml:space="preserve">titleDefense.cool.normal[2]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6616,7 +6616,7 @@
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.cool.normal[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.normal.cool[1]</t>
+          <t xml:space="preserve">titleLoss.cool.normal[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6648,7 +6648,7 @@
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.cool.normal[2]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.normal.cool[2]</t>
+          <t xml:space="preserve">titleLoss.cool.normal[2]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6680,7 +6680,7 @@
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.cool.normal[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.normal.cool[1]</t>
+          <t xml:space="preserve">titleWin.cool.normal[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6712,7 +6712,7 @@
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.cool.normal[2]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.normal.cool[2]</t>
+          <t xml:space="preserve">titleWin.cool.normal[2]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6744,7 +6744,7 @@
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6776,7 +6776,7 @@
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6808,7 +6808,7 @@
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6840,7 +6840,7 @@
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6872,7 +6872,7 @@
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6904,7 +6904,7 @@
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6919,7 +6919,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6936,7 +6936,7 @@
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6968,7 +6968,7 @@
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -7000,7 +7000,7 @@
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7032,7 +7032,7 @@
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7064,7 +7064,7 @@
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7096,7 +7096,7 @@
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.normal.cool[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7480,7 +7480,7 @@
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.normal.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.cool.normal[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.normal.cool[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.cool.normal[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7512,7 +7512,7 @@
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.normal.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.cool.normal[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.normal.cool[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.cool.normal[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7544,7 +7544,7 @@
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.normal.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.cool.normal[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.normal.cool[1]</t>
+          <t xml:space="preserve">GL-01.loss.cool.normal[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7576,7 +7576,7 @@
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.normal.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.cool.normal[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.normal.cool[1]</t>
+          <t xml:space="preserve">GL-01.win.cool.normal[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7608,7 +7608,7 @@
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.normal.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.cool.normal[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.normal.cool[1]</t>
+          <t xml:space="preserve">GL-02.cool.normal[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7640,7 +7640,7 @@
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.normal.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.cool.normal[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.normal.cool[1]</t>
+          <t xml:space="preserve">GL-03.down.cool.normal[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7672,7 +7672,7 @@
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.normal.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.cool.normal[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.normal.cool[1]</t>
+          <t xml:space="preserve">GL-03.up.cool.normal[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7704,7 +7704,7 @@
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.normal.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.cool.normal[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.normal.cool[1]</t>
+          <t xml:space="preserve">GL-04.cool.normal[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7736,7 +7736,7 @@
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.normal.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.cool.normal[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.normal.cool[1]</t>
+          <t xml:space="preserve">GL-05.cool.normal[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7768,7 +7768,7 @@
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.normal.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.cool.normal[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.normal.cool[1]</t>
+          <t xml:space="preserve">GL-06.cool.normal[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7800,7 +7800,7 @@
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.normal.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.cool.normal[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.normal.cool[1]</t>
+          <t xml:space="preserve">GL-07.cool.normal[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7832,7 +7832,7 @@
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.normal.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.cool.normal[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.normal.cool[1]</t>
+          <t xml:space="preserve">GL-08.cool.normal[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7864,7 +7864,7 @@
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.normal.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.cool.normal[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.normal.cool[1]</t>
+          <t xml:space="preserve">GL-09.cool.normal[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7896,7 +7896,7 @@
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.normal.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.cool.normal[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.normal.cool[1]</t>
+          <t xml:space="preserve">GL-10.cool.normal[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7928,7 +7928,7 @@
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.normal.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.cool.normal[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7943,7 +7943,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.normal.cool[1]</t>
+          <t xml:space="preserve">GL-11.cool.normal[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7960,7 +7960,7 @@
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7992,7 +7992,7 @@
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.cool[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.cool.normal[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.cool[1]</t>
+          <t xml:space="preserve">preFinal.cool.normal[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8024,7 +8024,7 @@
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.cool[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.cool.normal[2]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8039,7 +8039,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.cool[2]</t>
+          <t xml:space="preserve">preFinal.cool.normal[2]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8056,7 +8056,7 @@
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.cool[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.cool.normal[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.cool[1]</t>
+          <t xml:space="preserve">preMatch.cool.normal[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8088,7 +8088,7 @@
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.cool[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.cool.normal[2]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.cool[2]</t>
+          <t xml:space="preserve">preMatch.cool.normal[2]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8120,7 +8120,7 @@
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.cool[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.cool.normal[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.normal.cool[1]</t>
+          <t xml:space="preserve">survivor.cool.normal[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8152,7 +8152,7 @@
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.cool[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.cool.normal[2]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.normal.cool[2]</t>
+          <t xml:space="preserve">survivor.cool.normal[2]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8184,7 +8184,7 @@
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.cool[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.cool.normal[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.cool[1]</t>
+          <t xml:space="preserve">champion.cool.normal[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8216,7 +8216,7 @@
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.cool[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.cool.normal[2]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.cool[2]</t>
+          <t xml:space="preserve">champion.cool.normal[2]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8248,7 +8248,7 @@
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.cool[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.cool.normal[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.normal.cool[1]</t>
+          <t xml:space="preserve">defiant.cool.normal[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8280,7 +8280,7 @@
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.cool[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.cool.normal[2]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.normal.cool[2]</t>
+          <t xml:space="preserve">defiant.cool.normal[2]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8312,7 +8312,7 @@
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.cool[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.cool.normal[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.normal.cool[1]</t>
+          <t xml:space="preserve">gauntlet.cool.normal[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8344,7 +8344,7 @@
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.cool[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.cool.normal[2]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8359,7 +8359,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.normal.cool[2]</t>
+          <t xml:space="preserve">gauntlet.cool.normal[2]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8376,7 +8376,7 @@
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.normal.cool[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.cool.normal[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.cool[1]</t>
+          <t xml:space="preserve">champion.cool.normal[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8408,7 +8408,7 @@
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.normal.cool[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.cool.normal[2]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8423,7 +8423,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.cool[2]</t>
+          <t xml:space="preserve">champion.cool.normal[2]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8440,7 +8440,7 @@
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.normal.cool[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.cool.normal[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.normal.cool[1]</t>
+          <t xml:space="preserve">postLose.cool.normal[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8472,7 +8472,7 @@
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.normal.cool[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.cool.normal[2]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.normal.cool[2]</t>
+          <t xml:space="preserve">postLose.cool.normal[2]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8504,7 +8504,7 @@
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.normal.cool[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.cool.normal[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.normal.cool[1]</t>
+          <t xml:space="preserve">postMatchWin.cool.normal[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8536,7 +8536,7 @@
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.normal.cool[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.cool.normal[2]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.normal.cool[2]</t>
+          <t xml:space="preserve">postMatchWin.cool.normal[2]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8568,7 +8568,7 @@
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.normal.cool[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.cool.normal[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.normal.cool[1]</t>
+          <t xml:space="preserve">postWin.cool.normal[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8600,7 +8600,7 @@
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.normal.cool[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.cool.normal[2]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8615,7 +8615,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.normal.cool[2]</t>
+          <t xml:space="preserve">postWin.cool.normal[2]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8632,7 +8632,7 @@
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.normal.cool[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.cool.normal[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8647,7 +8647,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.cool[1]</t>
+          <t xml:space="preserve">preFinal.cool.normal[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8664,7 +8664,7 @@
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.normal.cool[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.cool.normal[2]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8679,7 +8679,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.cool[2]</t>
+          <t xml:space="preserve">preFinal.cool.normal[2]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8696,7 +8696,7 @@
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.normal.cool[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.cool.normal[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.cool[1]</t>
+          <t xml:space="preserve">preMatch.cool.normal[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8728,7 +8728,7 @@
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.normal.cool[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.cool.normal[2]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.cool[2]</t>
+          <t xml:space="preserve">preMatch.cool.normal[2]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8760,7 +8760,7 @@
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.normal.cool[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.cool.normal[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8775,7 +8775,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.normal.cool[1]</t>
+          <t xml:space="preserve">summon.cool.normal[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8792,7 +8792,7 @@
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.normal.cool[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.cool.normal[2]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8807,7 +8807,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.normal.cool[2]</t>
+          <t xml:space="preserve">summon.cool.normal[2]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8824,7 +8824,7 @@
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8856,7 +8856,7 @@
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8871,7 +8871,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8888,7 +8888,7 @@
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.normal.cool[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8920,7 +8920,7 @@
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.normal.cool[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.cool.normal[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8952,7 +8952,7 @@
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.normal.cool[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.cool.normal[2]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8984,7 +8984,7 @@
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.normal.cool[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.cool.normal[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -9016,7 +9016,7 @@
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.normal.cool[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.cool.normal[2]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9048,7 +9048,7 @@
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.normal.cool[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.cool.normal[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9063,7 +9063,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.normal.cool[1]</t>
+          <t xml:space="preserve">result_lose.cool.normal[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9080,7 +9080,7 @@
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.normal.cool[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.cool.normal[2]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.normal.cool[2]</t>
+          <t xml:space="preserve">result_lose.cool.normal[2]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9112,7 +9112,7 @@
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.normal.cool[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.cool.normal[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.normal.cool[1]</t>
+          <t xml:space="preserve">result_win.cool.normal[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9144,7 +9144,7 @@
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.normal.cool[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.cool.normal[2]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9159,7 +9159,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.normal.cool[2]</t>
+          <t xml:space="preserve">result_win.cool.normal[2]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9176,7 +9176,7 @@
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9208,7 +9208,7 @@
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.normal.cool[2]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9223,7 +9223,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9240,7 +9240,7 @@
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.normal.cool[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.cool.normal[3]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[3]</t>
+          <t xml:space="preserve">cool.normal[3]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9272,7 +9272,7 @@
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.normal.cool[1]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.cool.normal[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.normal.cool[1]</t>
+          <t xml:space="preserve">fighter.cool.normal[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9304,7 +9304,7 @@
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9319,7 +9319,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9336,7 +9336,7 @@
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.normal.cool[1]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9368,7 +9368,7 @@
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.normal.cool[2]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9383,7 +9383,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.cool[2]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">

--- a/セリフ編集/キャラタイプ別/クール×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/クール×ノーマル.xlsx
@@ -193,7 +193,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -205,7 +205,7 @@
     <row r="1">
       <c r="A1" t="inlineStr" s="11">
         <is>
-          <t xml:space="preserve">このタイプ(クール×ノーマル)に該当するキャラクター: 4名</t>
+          <t xml:space="preserve">このタイプ(クール×ノーマル)に該当するキャラクター: 3名</t>
         </is>
       </c>
     </row>
@@ -269,12 +269,12 @@
     <row r="6">
       <c r="A6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">松岡綾乃</t>
+          <t xml:space="preserve">柳沼英子</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Submission</t>
+          <t xml:space="preserve">Striker</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
@@ -283,28 +283,6 @@
         </is>
       </c>
       <c r="D6" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">引き出し上手</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">柳沼英子</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Striker</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Neutral</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">適応力</t>
         </is>
@@ -318,7 +296,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H283"/>
+  <dimension ref="A1:H285"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -4760,7 +4738,7 @@
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.cool.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.cool.normal[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4775,7 +4753,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.cool.normal[1]</t>
+          <t xml:space="preserve">autumnWarChampion.cool.normal[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4785,14 +4763,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう</t>
+          <t xml:space="preserve">団体の総合力が上だった。その結果だ。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.cool.normal[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4802,12 +4780,12 @@
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">mediaAward.cool.normal[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4817,14 +4795,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドーム…ね。来たか</t>
+          <t xml:space="preserve">…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.cool.normal[2]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.cool.normal[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4834,12 +4812,12 @@
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[2]</t>
+          <t xml:space="preserve">springTagChampion.cool.normal[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4849,14 +4827,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やることは、変わらない</t>
+          <t xml:space="preserve">役割を果たした結果だ。相棒にも敬意を表する。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.cool.normal[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4871,7 +4849,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[3]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4881,14 +4859,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…準備はできてる</t>
+          <t xml:space="preserve">ドーム…ね。来たか</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4898,12 +4876,12 @@
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4913,14 +4891,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…満員</t>
+          <t xml:space="preserve">…やることは、変わらない</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.cool.normal[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.cool.normal[3]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4930,12 +4908,12 @@
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[2]</t>
+          <t xml:space="preserve">cool.normal[3]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4945,14 +4923,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…客の声が、まだ耳に残ってる</t>
+          <t xml:space="preserve">…準備はできてる</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.cool.normal[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4967,7 +4945,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[3]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4977,14 +4955,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…忘れない。この景色は</t>
+          <t xml:space="preserve">…満員</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.cool.normal[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4994,29 +4972,29 @@
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.cool.normal[1]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そう。わかった</t>
+          <t xml:space="preserve">…客の声が、まだ耳に残ってる</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.cool.normal[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.cool.normal[3]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5026,29 +5004,29 @@
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.cool.normal[1]</t>
+          <t xml:space="preserve">cool.normal[3]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…メディアの話が来ている。出たい</t>
+          <t xml:space="preserve">…忘れない。この景色は</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.cool.normal[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.cool.normal[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5058,12 +5036,12 @@
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.cool.normal[2]</t>
+          <t xml:space="preserve">bonus_insult.cool.normal[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5073,14 +5051,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…出演の話。やらせてくれ</t>
+          <t xml:space="preserve">……そう。わかった</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.cool.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.cool.normal[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5095,7 +5073,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E4.cool.normal[1]</t>
+          <t xml:space="preserve">E1.cool.normal[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5105,14 +5083,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…スカウトの報告が来ている</t>
+          <t xml:space="preserve">…メディアの話が来ている。出たい</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.cool.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.cool.normal[2]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5127,7 +5105,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.cool.normal[1]</t>
+          <t xml:space="preserve">E1.cool.normal[2]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5137,14 +5115,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…他団体からオファーが来ている</t>
+          <t xml:space="preserve">…出演の話。やらせてくれ</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.cool.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.cool.normal[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5159,7 +5137,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.cool.normal[1]</t>
+          <t xml:space="preserve">E4.cool.normal[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5169,14 +5147,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（荷物をまとめて帰ろうとしている）</t>
+          <t xml:space="preserve">…スカウトの報告が来ている</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.cool.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.cool.normal[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5191,7 +5169,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.cool.normal[1]</t>
+          <t xml:space="preserve">E6.cool.normal[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5201,14 +5179,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（無言で佇んでいるが、周囲が気を遣って重い空気になっている）</t>
+          <t xml:space="preserve">…他団体からオファーが来ている</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.cool.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.cool.normal[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5223,7 +5201,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.cool.normal[1]</t>
+          <t xml:space="preserve">S_boycott.cool.normal[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5233,14 +5211,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに風景写真と「遠くへ」とだけ投稿。ファンがざわついている）</t>
+          <t xml:space="preserve">…………（荷物をまとめて帰ろうとしている）</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.cool.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.cool.normal[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5255,7 +5233,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.cool.normal[1]</t>
+          <t xml:space="preserve">S_grumble.cool.normal[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5265,14 +5243,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…タイトル戦を。組んでほしい</t>
+          <t xml:space="preserve">（無言で佇んでいるが、周囲が気を遣って重い空気になっている）</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.cool.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.cool.normal[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5287,7 +5265,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.cool.normal[1]</t>
+          <t xml:space="preserve">S_sns.cool.normal[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5297,14 +5275,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの人との試合を組んでほしい</t>
+          <t xml:space="preserve">（SNSに風景写真と「遠くへ」とだけ投稿。ファンがざわついている）</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.cool.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.cool.normal[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5319,7 +5297,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.cool.normal[1]</t>
+          <t xml:space="preserve">S1.cool.normal[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5329,14 +5307,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し、休みたい</t>
+          <t xml:space="preserve">…タイトル戦を。組んでほしい</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.cool.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.cool.normal[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5351,7 +5329,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.cool.normal[1]</t>
+          <t xml:space="preserve">S2.cool.normal[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5361,14 +5339,14 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…このままでは続けられない。考えてほしい</t>
+          <t xml:space="preserve">…あの人との試合を組んでほしい</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.cool.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.cool.normal[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5383,7 +5361,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.cool.normal[1]</t>
+          <t xml:space="preserve">S3.cool.normal[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5393,14 +5371,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（首を振って、口をつぐんだ）</t>
+          <t xml:space="preserve">…少し、休みたい</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.cool.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.cool.normal[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5415,7 +5393,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.cool.normal[1]</t>
+          <t xml:space="preserve">S4_direct.cool.normal[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5425,14 +5403,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…特訓の時間を。もらえるか</t>
+          <t xml:space="preserve">…このままでは続けられない。考えてほしい</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.cool.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.cool.normal[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5447,7 +5425,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.cool.normal[1]</t>
+          <t xml:space="preserve">S4_silent.cool.normal[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5457,14 +5435,14 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…後輩の指導を。任せてくれ</t>
+          <t xml:space="preserve">………（首を振って、口をつぐんだ）</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.cool.normal[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5474,29 +5452,29 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">S5.cool.normal[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。精一杯やる</t>
+          <t xml:space="preserve">…特訓の時間を。もらえるか</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.cool.normal[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.cool.normal[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5506,29 +5484,29 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[2]</t>
+          <t xml:space="preserve">S6.cool.normal[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…選んでくれるなら、全力で応える</t>
+          <t xml:space="preserve">…後輩の指導を。任せてくれ</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5538,7 +5516,7 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
@@ -5553,14 +5531,14 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よろしく</t>
+          <t xml:space="preserve">…よろしく。精一杯やる</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5570,7 +5548,7 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
@@ -5585,14 +5563,14 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……全力でやる</t>
+          <t xml:space="preserve">…選んでくれるなら、全力で応える</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5602,7 +5580,7 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
@@ -5617,14 +5595,14 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。力になる</t>
+          <t xml:space="preserve">……よろしく</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5634,7 +5612,7 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
@@ -5649,14 +5627,14 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…新しい環境か。悪くない。やる</t>
+          <t xml:space="preserve">……全力でやる</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5666,7 +5644,7 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
@@ -5681,14 +5659,14 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。やる</t>
+          <t xml:space="preserve">…よろしく。力になる</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5698,7 +5676,7 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
@@ -5713,14 +5691,14 @@
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…力になれるよう、精一杯やる</t>
+          <t xml:space="preserve">…新しい環境か。悪くない。やる</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5730,7 +5708,7 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
@@ -5745,14 +5723,14 @@
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……すぐ戻る</t>
+          <t xml:space="preserve">…よろしく。やる</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5762,7 +5740,7 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
@@ -5777,14 +5755,14 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……心配はいらない</t>
+          <t xml:space="preserve">…力になれるよう、精一杯やる</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5794,12 +5772,12 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.cool.normal[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5809,14 +5787,14 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……済んだ話だ。まだ気にする方がどうかしてる</t>
+          <t xml:space="preserve">……すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5826,12 +5804,12 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.cool.normal[1]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5841,14 +5819,14 @@
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……決着はついた。納得したとは、言ってない</t>
+          <t xml:space="preserve">……心配はいらない</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.cool.normal[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5863,7 +5841,7 @@
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.cool.normal[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.cool.normal[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5873,14 +5851,14 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。精一杯やる</t>
+          <t xml:space="preserve">……済んだ話だ。まだ気にする方がどうかしてる</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.cool.normal[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5895,7 +5873,7 @@
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.cool.normal[2]</t>
+          <t xml:space="preserve">bitterPrematch.behind.cool.normal[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5905,14 +5883,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…選んでくれるなら、全力で応える</t>
+          <t xml:space="preserve">……決着はついた。納得したとは、言ってない</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.cool.normal[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5927,7 +5905,7 @@
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.cool.normal[1]</t>
+          <t xml:space="preserve">draftInterest.cool.normal[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5937,14 +5915,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よろしく</t>
+          <t xml:space="preserve">…よろしく。精一杯やる</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.cool.normal[2]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5959,7 +5937,7 @@
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.cool.normal[2]</t>
+          <t xml:space="preserve">draftInterest.cool.normal[2]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5969,14 +5947,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……全力でやる</t>
+          <t xml:space="preserve">…選んでくれるなら、全力で応える</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.cool.normal[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5991,7 +5969,7 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.cool.normal[1]</t>
+          <t xml:space="preserve">draftJoin.cool.normal[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -6001,14 +5979,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…契約は契約。きっちり働く</t>
+          <t xml:space="preserve">……よろしく</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.cool.normal[2]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6023,7 +6001,7 @@
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.cool.normal[1]</t>
+          <t xml:space="preserve">draftJoin.cool.normal[2]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6033,14 +6011,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。力になる</t>
+          <t xml:space="preserve">……全力でやる</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.cool.normal[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6055,7 +6033,7 @@
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.cool.normal[2]</t>
+          <t xml:space="preserve">faGreeting.cool.normal[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6065,14 +6043,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…新しい環境か。悪くない。やる</t>
+          <t xml:space="preserve">…契約は契約。きっちり働く</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.cool.normal[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6087,7 +6065,7 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.cool.normal[1]</t>
+          <t xml:space="preserve">faSigning.cool.normal[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6097,14 +6075,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。やる</t>
+          <t xml:space="preserve">…よろしく。力になる</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.cool.normal[2]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6119,7 +6097,7 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.cool.normal[2]</t>
+          <t xml:space="preserve">faSigning.cool.normal[2]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6129,14 +6107,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…力になれるよう、精一杯やる</t>
+          <t xml:space="preserve">…新しい環境か。悪くない。やる</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.cool.normal[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6151,7 +6129,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.cool.normal[1]</t>
+          <t xml:space="preserve">faWelcome.cool.normal[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6161,14 +6139,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…調子はいい。今なら、何をやっても身につく</t>
+          <t xml:space="preserve">…よろしく。やる</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.cool.normal[2]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6183,7 +6161,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.cool.normal[1]</t>
+          <t xml:space="preserve">faWelcome.cool.normal[2]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6193,14 +6171,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体が重い。今日は、何をやっても素通りだ</t>
+          <t xml:space="preserve">…力になれるよう、精一杯やる</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.cool.normal[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6215,7 +6193,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.cool.normal[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.cool.normal[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6225,14 +6203,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…昨日と同じ動きだ。…なのに、入りが浅い</t>
+          <t xml:space="preserve">…調子はいい。今なら、何をやっても身につく</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.cool.normal[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6247,7 +6225,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.cool.normal[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.cool.normal[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6257,14 +6235,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……すぐ戻る</t>
+          <t xml:space="preserve">…体が重い。今日は、何をやっても素通りだ</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.cool.normal[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6279,7 +6257,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.cool.normal[2]</t>
+          <t xml:space="preserve">heatSelf.warm.cool.normal[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6289,14 +6267,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……心配はいらない</t>
+          <t xml:space="preserve">…昨日と同じ動きだ。…なのに、入りが浅い</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.cool.normal[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6311,7 +6289,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.cool.normal[1]</t>
+          <t xml:space="preserve">injury.cool.normal[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6321,14 +6299,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そうか。お世話になった</t>
+          <t xml:space="preserve">……すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.cool.normal[2]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6343,7 +6321,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.cool.normal[2]</t>
+          <t xml:space="preserve">injury.cool.normal[2]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6353,14 +6331,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここでの経験は、忘れない</t>
+          <t xml:space="preserve">……心配はいらない</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.cool.normal[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6375,7 +6353,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.cool.normal[1]</t>
+          <t xml:space="preserve">release.cool.normal[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6385,14 +6363,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…レンタルだが、手は抜かない。よろしく</t>
+          <t xml:space="preserve">……そうか。お世話になった</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.cool.normal[2]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6407,7 +6385,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.cool.normal[2]</t>
+          <t xml:space="preserve">release.cool.normal[2]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6417,14 +6395,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…短い間だ。よろしく</t>
+          <t xml:space="preserve">……ここでの経験は、忘れない</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.cool.normal[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6439,7 +6417,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.cool.normal[1]</t>
+          <t xml:space="preserve">rentalGreeting.cool.normal[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6449,14 +6427,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…話は受けた。あとは試合で</t>
+          <t xml:space="preserve">…レンタルだが、手は抜かない。よろしく</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.cool.normal[2]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6471,7 +6449,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.cool.normal[2]</t>
+          <t xml:space="preserve">rentalGreeting.cool.normal[2]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6481,14 +6459,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…期待は、悪くない</t>
+          <t xml:space="preserve">…短い間だ。よろしく</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.cool.normal[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6503,7 +6481,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.cool.normal[1]</t>
+          <t xml:space="preserve">scoutGreeting.cool.normal[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6513,14 +6491,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しい。だが、糧にはなった。次だ</t>
+          <t xml:space="preserve">…話は受けた。あとは試合で</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.cool.normal[2]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6535,7 +6513,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.cool.normal[2]</t>
+          <t xml:space="preserve">scoutGreeting.cool.normal[2]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6545,14 +6523,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…実力が足りなかった。強くなって戻る</t>
+          <t xml:space="preserve">…期待は、悪くない</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.cool.normal[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6567,7 +6545,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.cool.normal[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.cool.normal[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6577,14 +6555,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…防衛。…だが、まだ足りない</t>
+          <t xml:space="preserve">…悔しい。だが、糧にはなった。次だ</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.cool.normal[2]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6599,7 +6577,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.cool.normal[2]</t>
+          <t xml:space="preserve">titleChallengeLoss.cool.normal[2]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6609,14 +6587,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…守るたびに、このベルトの重さがわかる</t>
+          <t xml:space="preserve">…実力が足りなかった。強くなって戻る</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.cool.normal[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6631,7 +6609,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.cool.normal[1]</t>
+          <t xml:space="preserve">titleDefense.cool.normal[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6641,14 +6619,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…失った。だが、ここで戦い続ける</t>
+          <t xml:space="preserve">…防衛。…だが、まだ足りない</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.cool.normal[2]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6663,7 +6641,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.cool.normal[2]</t>
+          <t xml:space="preserve">titleDefense.cool.normal[2]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6673,14 +6651,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しい。チャンピオンとして、もっとやれたはずだ</t>
+          <t xml:space="preserve">…守るたびに、このベルトの重さがわかる</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.cool.normal[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6695,7 +6673,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.cool.normal[1]</t>
+          <t xml:space="preserve">titleLoss.cool.normal[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6705,14 +6683,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…獲った。チャンピオンだ</t>
+          <t xml:space="preserve">…失った。だが、ここで戦い続ける</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.cool.normal[2]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6727,7 +6705,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.cool.normal[2]</t>
+          <t xml:space="preserve">titleLoss.cool.normal[2]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6737,14 +6715,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…このベルトは手放さない</t>
+          <t xml:space="preserve">…悔しい。チャンピオンとして、もっとやれたはずだ</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.cool.normal[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6754,12 +6732,12 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">titleWin.cool.normal[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6769,14 +6747,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そうか。お世話になった</t>
+          <t xml:space="preserve">…獲った。チャンピオンだ</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.cool.normal[2]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6786,12 +6764,12 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[2]</t>
+          <t xml:space="preserve">titleWin.cool.normal[2]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6801,14 +6779,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここでの経験は、忘れない</t>
+          <t xml:space="preserve">…このベルトは手放さない</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6818,7 +6796,7 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
@@ -6833,14 +6811,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…レンタルだが、手は抜かない。よろしく</t>
+          <t xml:space="preserve">……そうか。お世話になった</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6850,7 +6828,7 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
@@ -6865,14 +6843,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…短い間だ。よろしく</t>
+          <t xml:space="preserve">……ここでの経験は、忘れない</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6882,7 +6860,7 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
@@ -6897,14 +6875,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しい。だが、糧にはなった。次だ</t>
+          <t xml:space="preserve">…レンタルだが、手は抜かない。よろしく</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6914,7 +6892,7 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
@@ -6929,14 +6907,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…実力が足りなかった。強くなって戻る</t>
+          <t xml:space="preserve">…短い間だ。よろしく</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6946,7 +6924,7 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
@@ -6961,14 +6939,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…防衛。…だが、まだ足りない</t>
+          <t xml:space="preserve">…悔しい。だが、糧にはなった。次だ</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6978,7 +6956,7 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
@@ -6993,14 +6971,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…守るたびに、このベルトの重さがわかる</t>
+          <t xml:space="preserve">…実力が足りなかった。強くなって戻る</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7010,7 +6988,7 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
@@ -7025,14 +7003,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…失った。だが、ここで戦い続ける</t>
+          <t xml:space="preserve">…防衛。…だが、まだ足りない</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7042,7 +7020,7 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
@@ -7057,14 +7035,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しい。チャンピオンとして、もっとやれたはずだ</t>
+          <t xml:space="preserve">…守るたびに、このベルトの重さがわかる</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7074,7 +7052,7 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
@@ -7089,14 +7067,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…獲った。チャンピオンだ</t>
+          <t xml:space="preserve">…失った。だが、ここで戦い続ける</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7106,7 +7084,7 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
@@ -7121,14 +7099,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…このベルトは手放さない</t>
+          <t xml:space="preserve">…悔しい。チャンピオンとして、もっとやれたはずだ</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7138,29 +7116,29 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…相容れない</t>
+          <t xml:space="preserve">…獲った。チャンピオンだ</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7170,29 +7148,29 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">距離感が…変わった</t>
+          <t xml:space="preserve">…このベルトは手放さない</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.cool[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7207,7 +7185,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.normal.cool[1]</t>
+          <t xml:space="preserve">bond_39_down.normal.cool[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7217,14 +7195,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いいバランスだ。やりやすい</t>
+          <t xml:space="preserve">…相容れない</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.cool[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7239,7 +7217,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.normal.cool[1]</t>
+          <t xml:space="preserve">bond_59_down.normal.cool[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7249,14 +7227,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">唯一の、本当の仲間だ</t>
+          <t xml:space="preserve">距離感が…変わった</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.cool[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7271,7 +7249,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.normal.cool[1]</t>
+          <t xml:space="preserve">bond_60_up.normal.cool[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7281,14 +7259,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…執着は、消えたか</t>
+          <t xml:space="preserve">いいバランスだ。やりやすい</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.cool[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7303,7 +7281,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.normal.cool[1]</t>
+          <t xml:space="preserve">bond_80_up.normal.cool[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7313,14 +7291,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この存在が…引っかかる</t>
+          <t xml:space="preserve">唯一の、本当の仲間だ</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.cool[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7335,7 +7313,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.normal.cool[1]</t>
+          <t xml:space="preserve">rivalry_29_down.normal.cool[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7345,14 +7323,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">倒すまで、止まれない</t>
+          <t xml:space="preserve">…執着は、消えたか</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.cool[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7367,7 +7345,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.normal.cool[1]</t>
+          <t xml:space="preserve">rivalry_30_up.normal.cool[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7377,14 +7355,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着をつけるまで、死んでも死にきれない</t>
+          <t xml:space="preserve">この存在が…引っかかる</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.cool[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7399,7 +7377,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.normal.cool[1]</t>
+          <t xml:space="preserve">rivalry_50_up.normal.cool[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7409,14 +7387,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここが…自分の場所だ</t>
+          <t xml:space="preserve">倒すまで、止まれない</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.cool[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7431,7 +7409,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.normal.cool[1]</t>
+          <t xml:space="preserve">rivalry_70_up.normal.cool[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7441,14 +7419,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここにいる理由が…もうない</t>
+          <t xml:space="preserve">決着をつけるまで、死んでも死にきれない</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.cool[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7463,7 +7441,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.normal.cool[1]</t>
+          <t xml:space="preserve">trust_above_75.normal.cool[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7473,14 +7451,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この環境に…疑問を感じ始めている</t>
+          <t xml:space="preserve">ここが…自分の場所だ</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.cool[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7490,12 +7468,12 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.cool.normal[1]</t>
+          <t xml:space="preserve">trust_below_20.normal.cool[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7505,14 +7483,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負けた。だが、後悔はない</t>
+          <t xml:space="preserve">ここにいる理由が…もうない</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.cool[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7522,12 +7500,12 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.cool.normal[1]</t>
+          <t xml:space="preserve">trust_below_35.normal.cool[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7537,14 +7515,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……完璧だった</t>
+          <t xml:space="preserve">この環境に…疑問を感じ始めている</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.cool.normal[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7559,7 +7537,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.cool.normal[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.cool.normal[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7569,14 +7547,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……足りないか</t>
+          <t xml:space="preserve">……負けた。だが、後悔はない</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.cool.normal[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7591,7 +7569,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.cool.normal[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.cool.normal[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7601,14 +7579,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った。それでいい</t>
+          <t xml:space="preserve">……完璧だった</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.cool.normal[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7623,7 +7601,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.cool.normal[1]</t>
+          <t xml:space="preserve">GL-01.loss.cool.normal[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7633,14 +7611,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……集中。あと一セット</t>
+          <t xml:space="preserve">……足りないか</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.cool.normal[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7655,7 +7633,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.cool.normal[1]</t>
+          <t xml:space="preserve">GL-01.win.cool.normal[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7665,14 +7643,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この状況は、よくない</t>
+          <t xml:space="preserve">……勝った。それでいい</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.cool.normal[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7687,7 +7665,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.cool.normal[1]</t>
+          <t xml:space="preserve">GL-02.cool.normal[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7697,14 +7675,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この環境は、悪くない</t>
+          <t xml:space="preserve">……集中。あと一セット</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.cool.normal[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7719,7 +7697,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.cool.normal[1]</t>
+          <t xml:space="preserve">GL-03.down.cool.normal[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7729,14 +7707,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…おかげで、ここにいる意味がある</t>
+          <t xml:space="preserve">……この状況は、よくない</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.cool.normal[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7751,7 +7729,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.cool.normal[1]</t>
+          <t xml:space="preserve">GL-03.up.cool.normal[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7761,14 +7739,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……情報は、自然と入ってくる</t>
+          <t xml:space="preserve">……この環境は、悪くない</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.cool.normal[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7783,7 +7761,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.cool.normal[1]</t>
+          <t xml:space="preserve">GL-04.cool.normal[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7793,14 +7771,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……出番がないのは、つらい</t>
+          <t xml:space="preserve">…おかげで、ここにいる意味がある</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.cool.normal[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7815,7 +7793,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.cool.normal[1]</t>
+          <t xml:space="preserve">GL-05.cool.normal[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7825,14 +7803,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……体が鈍い。これは…まずいな</t>
+          <t xml:space="preserve">……情報は、自然と入ってくる</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.cool.normal[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7847,7 +7825,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.cool.normal[1]</t>
+          <t xml:space="preserve">GL-06.cool.normal[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7857,14 +7835,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝てない。何が足りない</t>
+          <t xml:space="preserve">……出番がないのは、つらい</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.cool.normal[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7879,7 +7857,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.cool.normal[1]</t>
+          <t xml:space="preserve">GL-07.cool.normal[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7889,14 +7867,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負ける気がしない</t>
+          <t xml:space="preserve">……体が鈍い。これは…まずいな</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.cool.normal[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7911,7 +7889,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.cool.normal[1]</t>
+          <t xml:space="preserve">GL-08.cool.normal[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7921,14 +7899,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……じっとしているのが、一番つらい</t>
+          <t xml:space="preserve">……勝てない。何が足りない</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.cool.normal[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7943,7 +7921,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.cool.normal[1]</t>
+          <t xml:space="preserve">GL-09.cool.normal[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7953,14 +7931,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……認識の外。それだけ</t>
+          <t xml:space="preserve">……負ける気がしない</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.cool.normal[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7970,12 +7948,12 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">GL-10.cool.normal[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7985,14 +7963,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">調子は戻った。だが…確実に何かを掴んだ</t>
+          <t xml:space="preserve">……じっとしているのが、一番つらい</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.cool.normal[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -8002,29 +7980,29 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.cool.normal[1]</t>
+          <t xml:space="preserve">GL-11.cool.normal[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…身体の感覚は薄い。それでも、立てる。十分</t>
+          <t xml:space="preserve">……認識の外。それだけ</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.cool.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8034,29 +8012,29 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.cool.normal[2]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最後の一戦。ここまで来た。降りない</t>
+          <t xml:space="preserve">調子は戻った。だが…確実に何かを掴んだ</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.cool.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.cool.normal[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8071,7 +8049,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.cool.normal[1]</t>
+          <t xml:space="preserve">preFinal.cool.normal[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8081,14 +8059,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…相手は誰でもいい</t>
+          <t xml:space="preserve">…身体の感覚は薄い。それでも、立てる。十分</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.cool.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.cool.normal[2]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8103,7 +8081,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.cool.normal[2]</t>
+          <t xml:space="preserve">preFinal.cool.normal[2]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8113,14 +8091,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">真っ向から受ける。それだけ</t>
+          <t xml:space="preserve">…最後の一戦。ここまで来た。降りない</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.cool.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.cool.normal[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8135,7 +8113,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.cool.normal[1]</t>
+          <t xml:space="preserve">preMatch.cool.normal[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8145,14 +8123,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一人、落とした。息は上がってる。だが、退かない。次</t>
+          <t xml:space="preserve">…相手は誰でもいい</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.cool.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.cool.normal[2]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8167,7 +8145,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.cool.normal[2]</t>
+          <t xml:space="preserve">preMatch.cool.normal[2]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8177,14 +8155,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ立ってる。それで十分。次を出せ</t>
+          <t xml:space="preserve">真っ向から受ける。それだけ</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.cool.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.cool.normal[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8194,12 +8172,12 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.cool.normal[1]</t>
+          <t xml:space="preserve">survivor.cool.normal[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8209,14 +8187,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人の勝利。それ以上でも以下でもない</t>
+          <t xml:space="preserve">…一人、落とした。息は上がってる。だが、退かない。次</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.cool.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.cool.normal[2]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8226,12 +8204,12 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.cool.normal[2]</t>
+          <t xml:space="preserve">survivor.cool.normal[2]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8241,14 +8219,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人では成し得なかった。事実としてそう言える</t>
+          <t xml:space="preserve">…まだ立ってる。それで十分。次を出せ</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.cool.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.cool.normal[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8263,7 +8241,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.cool.normal[1]</t>
+          <t xml:space="preserve">champion.cool.normal[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8273,14 +8251,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">個人賞は事実として受け取る。だが、団体は負けた。次がある</t>
+          <t xml:space="preserve">三人の勝利。それ以上でも以下でもない</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.cool.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.cool.normal[2]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8295,7 +8273,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.cool.normal[2]</t>
+          <t xml:space="preserve">champion.cool.normal[2]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8305,14 +8283,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足りなかった。それだけ。次で取り返す</t>
+          <t xml:space="preserve">一人では成し得なかった。事実としてそう言える</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.cool.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.cool.normal[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8327,7 +8305,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.cool.normal[1]</t>
+          <t xml:space="preserve">defiant.cool.normal[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8337,14 +8315,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体の感覚はとっくに消えてる。それでも足だけは動いた。理由は知らない</t>
+          <t xml:space="preserve">個人賞は事実として受け取る。だが、団体は負けた。次がある</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.cool.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.cool.normal[2]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8359,7 +8337,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.cool.normal[2]</t>
+          <t xml:space="preserve">defiant.cool.normal[2]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8369,14 +8347,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人抜いたかより、最後に立っていたことだけが事実</t>
+          <t xml:space="preserve">足りなかった。それだけ。次で取り返す</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.cool.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.cool.normal[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8386,12 +8364,12 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.cool.normal[1]</t>
+          <t xml:space="preserve">gauntlet.cool.normal[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8401,14 +8379,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……優勝。……次のステージへ</t>
+          <t xml:space="preserve">身体の感覚はとっくに消えてる。それでも足だけは動いた。理由は知らない</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.cool.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.cool.normal[2]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8418,12 +8396,12 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.cool.normal[2]</t>
+          <t xml:space="preserve">gauntlet.cool.normal[2]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8433,14 +8411,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとう</t>
+          <t xml:space="preserve">何人抜いたかより、最後に立っていたことだけが事実</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.cool.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.cool.normal[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8455,7 +8433,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.cool.normal[1]</t>
+          <t xml:space="preserve">champion.cool.normal[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8465,14 +8443,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ足りない</t>
+          <t xml:space="preserve">……優勝。……次のステージへ</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.cool.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.cool.normal[2]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8487,7 +8465,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.cool.normal[2]</t>
+          <t xml:space="preserve">champion.cool.normal[2]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8497,14 +8475,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は負けない</t>
+          <t xml:space="preserve">……ありがとう</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.cool.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.cool.normal[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8519,7 +8497,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.cool.normal[1]</t>
+          <t xml:space="preserve">postLose.cool.normal[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8529,14 +8507,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一勝。次</t>
+          <t xml:space="preserve">……まだ足りない</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.cool.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.cool.normal[2]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8551,7 +8529,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.cool.normal[2]</t>
+          <t xml:space="preserve">postLose.cool.normal[2]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8561,14 +8539,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだだ</t>
+          <t xml:space="preserve">……次は負けない</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.cool.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.cool.normal[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8583,7 +8561,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.cool.normal[1]</t>
+          <t xml:space="preserve">postMatchWin.cool.normal[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8593,14 +8571,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悪くなかった</t>
+          <t xml:space="preserve">……一勝。次</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.cool.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.cool.normal[2]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8615,7 +8593,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.cool.normal[2]</t>
+          <t xml:space="preserve">postMatchWin.cool.normal[2]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8625,14 +8603,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……収穫はあった</t>
+          <t xml:space="preserve">……まだだ</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.cool.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.cool.normal[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8647,7 +8625,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.cool.normal[1]</t>
+          <t xml:space="preserve">postWin.cool.normal[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8657,14 +8635,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……決勝。全て出す</t>
+          <t xml:space="preserve">……悪くなかった</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.cool.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.cool.normal[2]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8679,7 +8657,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.cool.normal[2]</t>
+          <t xml:space="preserve">postWin.cool.normal[2]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8689,14 +8667,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……最後の一戦</t>
+          <t xml:space="preserve">……収穫はあった</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.cool.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.cool.normal[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8711,7 +8689,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.cool.normal[1]</t>
+          <t xml:space="preserve">preFinal.cool.normal[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8721,14 +8699,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……集中する</t>
+          <t xml:space="preserve">……決勝。全て出す</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.cool.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.cool.normal[2]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8743,7 +8721,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.cool.normal[2]</t>
+          <t xml:space="preserve">preFinal.cool.normal[2]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8753,14 +8731,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……行く</t>
+          <t xml:space="preserve">……最後の一戦</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.cool.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.cool.normal[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8775,7 +8753,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.cool.normal[1]</t>
+          <t xml:space="preserve">preMatch.cool.normal[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8785,14 +8763,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……出る。それだけだ</t>
+          <t xml:space="preserve">……集中する</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.cool.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.cool.normal[2]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8807,7 +8785,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.cool.normal[2]</t>
+          <t xml:space="preserve">preMatch.cool.normal[2]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8817,14 +8795,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝つだけだ</t>
+          <t xml:space="preserve">……行く</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.cool.normal[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8834,12 +8812,12 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">summon.cool.normal[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8849,14 +8827,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……受けて立つ。全力だ</t>
+          <t xml:space="preserve">……出る。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.cool.normal[2]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8866,12 +8844,12 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">summon.cool.normal[2]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8881,14 +8859,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここが頂点。……でも、まだ先がある</t>
+          <t xml:space="preserve">……勝つだけだ</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.cool.normal[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8898,12 +8876,12 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[2]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8913,14 +8891,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った。（静かにベルトを掲げる）</t>
+          <t xml:space="preserve">……受けて立つ。全力だ</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.cool.normal[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8930,7 +8908,7 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
@@ -8945,14 +8923,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……挑戦する。受けろ</t>
+          <t xml:space="preserve">……ここが頂点。……でも、まだ先がある</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.cool.normal[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8962,7 +8940,7 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
@@ -8977,14 +8955,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……実力で語る。それだけだ</t>
+          <t xml:space="preserve">……勝った。（静かにベルトを掲げる）</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.cool.normal[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.cool.normal[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8994,7 +8972,7 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
@@ -9009,14 +8987,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……臆病者</t>
+          <t xml:space="preserve">……挑戦する。受けろ</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.cool.normal[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.cool.normal[2]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9026,7 +9004,7 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
@@ -9041,14 +9019,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……逃げたか</t>
+          <t xml:space="preserve">……実力で語る。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.cool.normal[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.cool.normal[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9058,12 +9036,12 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.cool.normal[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9073,14 +9051,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負けた。……受け止める</t>
+          <t xml:space="preserve">……臆病者</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.cool.normal[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.cool.normal[2]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9090,12 +9068,12 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.cool.normal[2]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9105,14 +9083,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は違う</t>
+          <t xml:space="preserve">……逃げたか</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.cool.normal[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.cool.normal[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9127,7 +9105,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.cool.normal[1]</t>
+          <t xml:space="preserve">result_lose.cool.normal[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9137,14 +9115,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った。それが全てだ</t>
+          <t xml:space="preserve">……負けた。……受け止める</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.cool.normal[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.cool.normal[2]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9159,7 +9137,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.cool.normal[2]</t>
+          <t xml:space="preserve">result_lose.cool.normal[2]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9169,14 +9147,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悪くない</t>
+          <t xml:space="preserve">……次は違う</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.cool.normal[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9186,12 +9164,12 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">result_win.cool.normal[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9201,14 +9179,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…団体の看板、背負えた</t>
+          <t xml:space="preserve">……勝った。それが全てだ</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.cool.normal[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.cool.normal[2]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9218,12 +9196,12 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[2]</t>
+          <t xml:space="preserve">result_win.cool.normal[2]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9233,14 +9211,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝った。それだけ</t>
+          <t xml:space="preserve">……悪くない</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.cool.normal[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9255,7 +9233,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[3]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9265,14 +9243,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った。それでいい</t>
+          <t xml:space="preserve">…団体の看板、背負えた</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.cool.normal[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9282,29 +9260,29 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.cool.normal[1]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……終わったか。……悪くない</t>
+          <t xml:space="preserve">…勝った。それだけ</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.cool.normal[3]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9314,29 +9292,29 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">cool.normal[3]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…契約は契約。きっちり働く</t>
+          <t xml:space="preserve">……勝った。それでいい</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.cool.normal[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9346,59 +9324,123 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">fighter.cool.normal[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…話は受けた。あとは試合で</t>
+          <t xml:space="preserve">……終わったか。……悪くない</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">FA_GREETING_LINES.cool.normal[1]</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cool.normal[1]</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…契約は契約。きっちり働く</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="40" customHeight="1">
+      <c r="A284" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.cool.normal[1]</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cool.normal[1]</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…話は受けた。あとは試合で</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="40" customHeight="1">
+      <c r="A285" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.cool.normal[2]</t>
         </is>
       </c>
-      <c r="B283" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr" s="2">
+      <c r="B285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr" s="12">
+      <c r="D285" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
-      <c r="E283" t="inlineStr" s="2">
+      <c r="E285" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F283" t="inlineStr" s="3">
+      <c r="F285" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…期待は、悪くない</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H283"/>
+  <autoFilter ref="A1:H285"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/クール×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/クール×ノーマル.xlsx
@@ -296,7 +296,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H285"/>
+  <dimension ref="A1:H292"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3810,7 +3810,7 @@
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.cool.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_accept.cool.normal[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.cool.normal[1]</t>
+          <t xml:space="preserve">decline_accept.cool.normal[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3835,14 +3835,14 @@
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。これからも、よろしく</t>
+          <t xml:space="preserve">……妥当だ。数字で下がったなら、数字で戻す。それだけ</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.cool.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_hold.cool.normal[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.cool.normal[1]</t>
+          <t xml:space="preserve">decline_hold.cool.normal[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3867,14 +3867,14 @@
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…上がるなら、ありがたい。…やるよ</t>
+          <t xml:space="preserve">……下げないのか。……普通は下げる場面だ。その普通じゃない分、返す</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.cool.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_open.cool.normal[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.cool.normal[1]</t>
+          <t xml:space="preserve">decline_open.cool.normal[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3899,14 +3899,14 @@
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうか。…分かりました</t>
+          <t xml:space="preserve">{tenure}……落ちてるのは自覚してる。……で、どれだけ下がる</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.cool.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_strict.cool.normal[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.cool.normal[1]</t>
+          <t xml:space="preserve">decline_strict.cool.normal[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3931,14 +3931,14 @@
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……考えさせてくれ</t>
+          <t xml:space="preserve">……そこまでやるんだ。……分かった。もう何も言わない</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.cool.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_accept.cool.normal[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.cool.normal[1]</t>
+          <t xml:space="preserve">decline_voluntary_accept.cool.normal[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3963,14 +3963,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうか。分かった。…少し、残念だ</t>
+          <t xml:space="preserve">……うん、それでいい。……変に庇われるより、ずっと楽だ</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.cool.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_hold.cool.normal[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.cool.normal[1]</t>
+          <t xml:space="preserve">decline_voluntary_hold.cool.normal[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -3995,14 +3995,14 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。手短に言う。……辞めます。もう決めた</t>
+          <t xml:space="preserve">……下げないのか。……変な人だ。なら、下げさせない働きをする</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.cool.normal[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_open.cool.normal[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.cool.normal[2]</t>
+          <t xml:space="preserve">decline_voluntary_open.cool.normal[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4027,14 +4027,14 @@
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…世話になった。……でも、もう続けられない</t>
+          <t xml:space="preserve">社長。……全盛期は過ぎた。査定、下げていい。……その分、若いのに回して</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.cool.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.cool.normal[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.cool.normal[1]</t>
+          <t xml:space="preserve">raise_accept.cool.normal[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4059,14 +4059,14 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…聞いてくれるんだ。{record}…新しい場所で、試したい</t>
+          <t xml:space="preserve">…ありがとう。これからも、よろしく</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.cool.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.cool.normal[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.cool.normal[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.cool.normal[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4091,14 +4091,14 @@
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長。{tenure}…ここを、出ようと思う</t>
+          <t xml:space="preserve">…上がるなら、ありがたい。…やるよ</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.cool.normal[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.cool.normal[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.cool.normal[2]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.cool.normal[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4123,14 +4123,14 @@
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…色々、考えた。{tenure}…外でやってみたい</t>
+          <t xml:space="preserve">…そうか。…分かりました</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.cool.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.cool.normal[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.cool.normal[1]</t>
+          <t xml:space="preserve">raise_open.cool.normal[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4155,14 +4155,14 @@
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…分かった。{tenure_farewell}{rivalry}…世話になった</t>
+          <t xml:space="preserve">……考えさせてくれ</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.cool.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.cool.normal[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.cool.normal[1]</t>
+          <t xml:space="preserve">raise_refuse.cool.normal[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4187,14 +4187,14 @@
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがたい。…でも、もう決めた。…ごめん</t>
+          <t xml:space="preserve">…そうか。分かった。…少し、残念だ</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.cool.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.cool.normal[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.cool.normal[1]</t>
+          <t xml:space="preserve">sudden_departure.cool.normal[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4219,14 +4219,14 @@
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そこまでしてくれるんだ。…分かった。もう少し、やってみる</t>
+          <t xml:space="preserve">社長。手短に言う。……辞めます。もう決めた</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.cool.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.cool.normal[2]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.cool.normal[1]</t>
+          <t xml:space="preserve">sudden_departure.cool.normal[2]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4251,14 +4251,14 @@
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……条件次第だ</t>
+          <t xml:space="preserve">…世話になった。……でも、もう続けられない</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.cool.normal[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4268,29 +4268,29 @@
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">transfer_listen.cool.normal[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……成長を、実感している</t>
+          <t xml:space="preserve">…聞いてくれるんだ。{record}…新しい場所で、試したい</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.cool.normal[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4300,29 +4300,29 @@
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">transfer_open.cool.normal[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……何かが、変わり始めている</t>
+          <t xml:space="preserve">…社長。{tenure}…ここを、出ようと思う</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.cool.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.cool.normal[2]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4332,29 +4332,29 @@
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh.cool.normal[1]</t>
+          <t xml:space="preserve">transfer_open.cool.normal[2]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…調子はいい。今なら、何をやっても身につく</t>
+          <t xml:space="preserve">…色々、考えた。{tenure}…外でやってみたい</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.cool.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.cool.normal[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4364,29 +4364,29 @@
       </c>
       <c r="C127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy.cool.normal[1]</t>
+          <t xml:space="preserve">transfer_release.cool.normal[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体が重い。今日は、何をやっても素通りだ</t>
+          <t xml:space="preserve">…分かった。{tenure_farewell}{rivalry}…世話になった</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.cool.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.cool.normal[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4396,29 +4396,29 @@
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm.cool.normal[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.cool.normal[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…昨日と同じ動きだ。…なのに、入りが浅い</t>
+          <t xml:space="preserve">…ありがたい。…でも、もう決めた。…ごめん</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.cool.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.cool.normal[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4428,29 +4428,29 @@
       </c>
       <c r="C129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.cool.normal[1]</t>
+          <t xml:space="preserve">transfer_retain_success.cool.normal[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここが、天井か</t>
+          <t xml:space="preserve">…そこまでしてくれるんだ。…分かった。もう少し、やってみる</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.cool.normal[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.cool.normal[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4460,29 +4460,29 @@
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.cool.normal[1]</t>
+          <t xml:space="preserve">start.cool.normal[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一つの壁を、越えた</t>
+          <t xml:space="preserve">……条件次第だ</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.cool.normal[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4492,12 +4492,12 @@
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.cool.normal[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4507,14 +4507,14 @@
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……手応えは、ある</t>
+          <t xml:space="preserve">……成長を、実感している</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.cool.normal[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.cool.normal[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4539,14 +4539,14 @@
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この先に何があるのか。…見てみたい</t>
+          <t xml:space="preserve">……何かが、変わり始めている</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.cool.normal[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.cool.normal[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.cool.normal[1]</t>
+          <t xml:space="preserve">fresh.cool.normal[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4571,14 +4571,14 @@
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……認知されてきた、か</t>
+          <t xml:space="preserve">…調子はいい。今なら、何をやっても身につく</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.cool.normal[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.cool.normal[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4588,12 +4588,12 @@
       </c>
       <c r="C134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.cool.normal[1]</t>
+          <t xml:space="preserve">heavy.cool.normal[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4603,14 +4603,14 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……背負うものが増えた。…それでいい</t>
+          <t xml:space="preserve">…体が重い。今日は、何をやっても素通りだ</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.cool.normal[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="C135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">warm.cool.normal[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4635,14 +4635,14 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……何のために戦っているのか、見えなくなった</t>
+          <t xml:space="preserve">…昨日と同じ動きだ。…なのに、入りが浅い</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.cool.normal[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4652,12 +4652,12 @@
       </c>
       <c r="C136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">cap_reached.cool.normal[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4667,14 +4667,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……思い出した。戦う理由を</t>
+          <t xml:space="preserve">……ここが、天井か</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.cool.normal[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">ovr_elite.cool.normal[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4699,14 +4699,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……戻ってきた。この感覚だ</t>
+          <t xml:space="preserve">……一つの壁を、越えた</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.cool.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.cool.normal[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4716,12 +4716,12 @@
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.cool.normal[1]</t>
+          <t xml:space="preserve">ovr_growth.cool.normal[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4731,14 +4731,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……最近、噛み合わない</t>
+          <t xml:space="preserve">……手応えは、ある</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.cool.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.cool.normal[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4748,29 +4748,29 @@
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">autumnWarChampion.cool.normal[1]</t>
+          <t xml:space="preserve">ovr_legend.cool.normal[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体の総合力が上だった。その結果だ。</t>
+          <t xml:space="preserve">……この先に何があるのか。…見てみたい</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.cool.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.cool.normal[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4780,29 +4780,29 @@
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.cool.normal[1]</t>
+          <t xml:space="preserve">pop_growth.cool.normal[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう</t>
+          <t xml:space="preserve">……認知されてきた、か</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.springTagChampion.cool.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.cool.normal[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4812,29 +4812,29 @@
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">springTagChampion.cool.normal[1]</t>
+          <t xml:space="preserve">pop_star.cool.normal[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">役割を果たした結果だ。相棒にも敬意を表する。</t>
+          <t xml:space="preserve">……背負うものが増えた。…それでいい</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="12">
@@ -4854,19 +4854,19 @@
       </c>
       <c r="E142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドーム…ね。来たか</t>
+          <t xml:space="preserve">……何のために戦っているのか、見えなくなった</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.cool.normal[2]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4876,29 +4876,29 @@
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[2]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やることは、変わらない</t>
+          <t xml:space="preserve">……思い出した。戦う理由を</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.cool.normal[3]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4908,29 +4908,29 @@
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[3]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…準備はできてる</t>
+          <t xml:space="preserve">……戻ってきた。この感覚だ</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.cool.normal[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4940,29 +4940,29 @@
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">defeat.cool.normal[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…満員</t>
+          <t xml:space="preserve">……最近、噛み合わない</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.cool.normal[2]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.cool.normal[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[2]</t>
+          <t xml:space="preserve">autumnWarChampion.cool.normal[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -4987,14 +4987,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…客の声が、まだ耳に残ってる</t>
+          <t xml:space="preserve">団体の総合力が上だった。その結果だ。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.cool.normal[3]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.cool.normal[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[3]</t>
+          <t xml:space="preserve">mediaAward.cool.normal[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5019,14 +5019,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…忘れない。この景色は</t>
+          <t xml:space="preserve">…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.cool.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.cool.normal[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5036,29 +5036,29 @@
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.cool.normal[1]</t>
+          <t xml:space="preserve">springTagChampion.cool.normal[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そう。わかった</t>
+          <t xml:space="preserve">役割を果たした結果だ。相棒にも敬意を表する。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.cool.normal[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5068,29 +5068,29 @@
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.cool.normal[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…メディアの話が来ている。出たい</t>
+          <t xml:space="preserve">ドーム…ね。来たか</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.cool.normal[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5100,29 +5100,29 @@
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.cool.normal[2]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…出演の話。やらせてくれ</t>
+          <t xml:space="preserve">…やることは、変わらない</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.cool.normal[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.cool.normal[3]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5132,29 +5132,29 @@
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E4.cool.normal[1]</t>
+          <t xml:space="preserve">cool.normal[3]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…スカウトの報告が来ている</t>
+          <t xml:space="preserve">…準備はできてる</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.cool.normal[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5164,29 +5164,29 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.cool.normal[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…他団体からオファーが来ている</t>
+          <t xml:space="preserve">…満員</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.cool.normal[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5196,29 +5196,29 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.cool.normal[1]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（荷物をまとめて帰ろうとしている）</t>
+          <t xml:space="preserve">…客の声が、まだ耳に残ってる</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.cool.normal[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.cool.normal[3]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5228,29 +5228,29 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.cool.normal[1]</t>
+          <t xml:space="preserve">cool.normal[3]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（無言で佇んでいるが、周囲が気を遣って重い空気になっている）</t>
+          <t xml:space="preserve">…忘れない。この景色は</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.cool.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.cool.normal[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5260,12 +5260,12 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.cool.normal[1]</t>
+          <t xml:space="preserve">bonus_insult.cool.normal[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5275,14 +5275,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに風景写真と「遠くへ」とだけ投稿。ファンがざわついている）</t>
+          <t xml:space="preserve">……そう。わかった</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.cool.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.cool.normal[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.cool.normal[1]</t>
+          <t xml:space="preserve">E1.cool.normal[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5307,14 +5307,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…タイトル戦を。組んでほしい</t>
+          <t xml:space="preserve">…メディアの話が来ている。出たい</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.cool.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.cool.normal[2]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.cool.normal[1]</t>
+          <t xml:space="preserve">E1.cool.normal[2]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5339,14 +5339,14 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの人との試合を組んでほしい</t>
+          <t xml:space="preserve">…出演の話。やらせてくれ</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.cool.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.cool.normal[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.cool.normal[1]</t>
+          <t xml:space="preserve">E4.cool.normal[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5371,14 +5371,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し、休みたい</t>
+          <t xml:space="preserve">…スカウトの報告が来ている</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.cool.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.cool.normal[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.cool.normal[1]</t>
+          <t xml:space="preserve">E6.cool.normal[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5403,14 +5403,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…このままでは続けられない。考えてほしい</t>
+          <t xml:space="preserve">…他団体からオファーが来ている</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.cool.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.cool.normal[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.cool.normal[1]</t>
+          <t xml:space="preserve">S_boycott.cool.normal[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5435,14 +5435,14 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（首を振って、口をつぐんだ）</t>
+          <t xml:space="preserve">…………（荷物をまとめて帰ろうとしている）</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.cool.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.cool.normal[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.cool.normal[1]</t>
+          <t xml:space="preserve">S_grumble.cool.normal[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5467,14 +5467,14 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…特訓の時間を。もらえるか</t>
+          <t xml:space="preserve">（無言で佇んでいるが、周囲が気を遣って重い空気になっている）</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.cool.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.cool.normal[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.cool.normal[1]</t>
+          <t xml:space="preserve">S_sns.cool.normal[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5499,14 +5499,14 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…後輩の指導を。任せてくれ</t>
+          <t xml:space="preserve">（SNSに風景写真と「遠くへ」とだけ投稿。ファンがざわついている）</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.cool.normal[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5516,29 +5516,29 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">S1.cool.normal[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。精一杯やる</t>
+          <t xml:space="preserve">…タイトル戦を。組んでほしい</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.cool.normal[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.cool.normal[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5548,29 +5548,29 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[2]</t>
+          <t xml:space="preserve">S2.cool.normal[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…選んでくれるなら、全力で応える</t>
+          <t xml:space="preserve">…あの人との試合を組んでほしい</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.cool.normal[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5580,29 +5580,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">S3.cool.normal[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よろしく</t>
+          <t xml:space="preserve">…少し、休みたい</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.cool.normal[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.cool.normal[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5612,29 +5612,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[2]</t>
+          <t xml:space="preserve">S4_direct.cool.normal[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……全力でやる</t>
+          <t xml:space="preserve">…このままでは続けられない。考えてほしい</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.cool.normal[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5644,29 +5644,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">S4_silent.cool.normal[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。力になる</t>
+          <t xml:space="preserve">………（首を振って、口をつぐんだ）</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.cool.normal[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.cool.normal[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5676,29 +5676,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[2]</t>
+          <t xml:space="preserve">S5.cool.normal[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…新しい環境か。悪くない。やる</t>
+          <t xml:space="preserve">…特訓の時間を。もらえるか</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.cool.normal[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5708,29 +5708,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">S6.cool.normal[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。やる</t>
+          <t xml:space="preserve">…後輩の指導を。任せてくれ</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[2]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5755,14 +5755,14 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…力になれるよう、精一杯やる</t>
+          <t xml:space="preserve">…よろしく。精一杯やる</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5787,14 +5787,14 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……すぐ戻る</t>
+          <t xml:space="preserve">…選んでくれるなら、全力で応える</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[2]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5819,14 +5819,14 @@
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……心配はいらない</t>
+          <t xml:space="preserve">……よろしく</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5836,12 +5836,12 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.cool.normal[1]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5851,14 +5851,14 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……済んだ話だ。まだ気にする方がどうかしてる</t>
+          <t xml:space="preserve">……全力でやる</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.cool.normal[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5883,14 +5883,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……決着はついた。納得したとは、言ってない</t>
+          <t xml:space="preserve">…よろしく。力になる</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.cool.normal[1]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5915,14 +5915,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。精一杯やる</t>
+          <t xml:space="preserve">…新しい環境か。悪くない。やる</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.cool.normal[2]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5947,14 +5947,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…選んでくれるなら、全力で応える</t>
+          <t xml:space="preserve">…よろしく。やる</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5964,12 +5964,12 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.cool.normal[1]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5979,14 +5979,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よろしく</t>
+          <t xml:space="preserve">…力になれるよう、精一杯やる</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.cool.normal[2]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6011,14 +6011,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……全力でやる</t>
+          <t xml:space="preserve">……すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6028,12 +6028,12 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.cool.normal[1]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6043,14 +6043,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…契約は契約。きっちり働く</t>
+          <t xml:space="preserve">……心配はいらない</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.cool.normal[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.cool.normal[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.cool.normal[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6075,14 +6075,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。力になる</t>
+          <t xml:space="preserve">……済んだ話だ。まだ気にする方がどうかしてる</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.cool.normal[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.cool.normal[2]</t>
+          <t xml:space="preserve">bitterPrematch.behind.cool.normal[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6107,14 +6107,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…新しい環境か。悪くない。やる</t>
+          <t xml:space="preserve">……決着はついた。納得したとは、言ってない</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.cool.normal[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.cool.normal[1]</t>
+          <t xml:space="preserve">draftInterest.cool.normal[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6139,14 +6139,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。やる</t>
+          <t xml:space="preserve">…よろしく。精一杯やる</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.cool.normal[2]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.cool.normal[2]</t>
+          <t xml:space="preserve">draftInterest.cool.normal[2]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6171,14 +6171,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…力になれるよう、精一杯やる</t>
+          <t xml:space="preserve">…選んでくれるなら、全力で応える</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.cool.normal[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.cool.normal[1]</t>
+          <t xml:space="preserve">draftJoin.cool.normal[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6203,14 +6203,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…調子はいい。今なら、何をやっても身につく</t>
+          <t xml:space="preserve">……よろしく</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.cool.normal[2]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.cool.normal[1]</t>
+          <t xml:space="preserve">draftJoin.cool.normal[2]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6235,14 +6235,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体が重い。今日は、何をやっても素通りだ</t>
+          <t xml:space="preserve">……全力でやる</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.cool.normal[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.cool.normal[1]</t>
+          <t xml:space="preserve">faGreeting.cool.normal[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6267,14 +6267,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…昨日と同じ動きだ。…なのに、入りが浅い</t>
+          <t xml:space="preserve">…契約は契約。きっちり働く</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.cool.normal[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.cool.normal[1]</t>
+          <t xml:space="preserve">faSigning.cool.normal[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6299,14 +6299,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……すぐ戻る</t>
+          <t xml:space="preserve">…よろしく。力になる</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.cool.normal[2]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.cool.normal[2]</t>
+          <t xml:space="preserve">faSigning.cool.normal[2]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6331,14 +6331,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……心配はいらない</t>
+          <t xml:space="preserve">…新しい環境か。悪くない。やる</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.cool.normal[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.cool.normal[1]</t>
+          <t xml:space="preserve">faWelcome.cool.normal[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6363,14 +6363,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そうか。お世話になった</t>
+          <t xml:space="preserve">…よろしく。やる</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.cool.normal[2]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.cool.normal[2]</t>
+          <t xml:space="preserve">faWelcome.cool.normal[2]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6395,14 +6395,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここでの経験は、忘れない</t>
+          <t xml:space="preserve">…力になれるよう、精一杯やる</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.cool.normal[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.cool.normal[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.cool.normal[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6427,14 +6427,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…レンタルだが、手は抜かない。よろしく</t>
+          <t xml:space="preserve">…調子はいい。今なら、何をやっても身につく</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.cool.normal[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.cool.normal[2]</t>
+          <t xml:space="preserve">heatSelf.heavy.cool.normal[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6459,14 +6459,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…短い間だ。よろしく</t>
+          <t xml:space="preserve">…体が重い。今日は、何をやっても素通りだ</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.cool.normal[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.cool.normal[1]</t>
+          <t xml:space="preserve">heatSelf.warm.cool.normal[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6491,14 +6491,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…話は受けた。あとは試合で</t>
+          <t xml:space="preserve">…昨日と同じ動きだ。…なのに、入りが浅い</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.cool.normal[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.cool.normal[2]</t>
+          <t xml:space="preserve">injury.cool.normal[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6523,14 +6523,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…期待は、悪くない</t>
+          <t xml:space="preserve">……すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.cool.normal[2]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.cool.normal[1]</t>
+          <t xml:space="preserve">injury.cool.normal[2]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6555,14 +6555,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しい。だが、糧にはなった。次だ</t>
+          <t xml:space="preserve">……心配はいらない</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.cool.normal[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6577,7 +6577,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.cool.normal[2]</t>
+          <t xml:space="preserve">release.cool.normal[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6587,14 +6587,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…実力が足りなかった。強くなって戻る</t>
+          <t xml:space="preserve">……そうか。お世話になった</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.cool.normal[2]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.cool.normal[1]</t>
+          <t xml:space="preserve">release.cool.normal[2]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6619,14 +6619,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…防衛。…だが、まだ足りない</t>
+          <t xml:space="preserve">……ここでの経験は、忘れない</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.cool.normal[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.cool.normal[2]</t>
+          <t xml:space="preserve">rentalGreeting.cool.normal[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6651,14 +6651,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…守るたびに、このベルトの重さがわかる</t>
+          <t xml:space="preserve">…レンタルだが、手は抜かない。よろしく</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.cool.normal[2]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.cool.normal[1]</t>
+          <t xml:space="preserve">rentalGreeting.cool.normal[2]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6683,14 +6683,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…失った。だが、ここで戦い続ける</t>
+          <t xml:space="preserve">…短い間だ。よろしく</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.cool.normal[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.cool.normal[2]</t>
+          <t xml:space="preserve">scoutGreeting.cool.normal[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6715,14 +6715,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しい。チャンピオンとして、もっとやれたはずだ</t>
+          <t xml:space="preserve">…話は受けた。あとは試合で</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.cool.normal[2]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.cool.normal[1]</t>
+          <t xml:space="preserve">scoutGreeting.cool.normal[2]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6747,14 +6747,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…獲った。チャンピオンだ</t>
+          <t xml:space="preserve">…期待は、悪くない</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.cool.normal[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6769,7 +6769,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.cool.normal[2]</t>
+          <t xml:space="preserve">titleChallengeLoss.cool.normal[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6779,14 +6779,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…このベルトは手放さない</t>
+          <t xml:space="preserve">…悔しい。だが、糧にはなった。次だ</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.cool.normal[2]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.cool.normal[2]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6811,14 +6811,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そうか。お世話になった</t>
+          <t xml:space="preserve">…実力が足りなかった。強くなって戻る</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.cool.normal[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[2]</t>
+          <t xml:space="preserve">titleDefense.cool.normal[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6843,14 +6843,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここでの経験は、忘れない</t>
+          <t xml:space="preserve">…防衛。…だが、まだ足りない</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.cool.normal[2]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6860,12 +6860,12 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">titleDefense.cool.normal[2]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6875,14 +6875,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…レンタルだが、手は抜かない。よろしく</t>
+          <t xml:space="preserve">…守るたびに、このベルトの重さがわかる</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.cool.normal[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[2]</t>
+          <t xml:space="preserve">titleLoss.cool.normal[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6907,14 +6907,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…短い間だ。よろしく</t>
+          <t xml:space="preserve">…失った。だが、ここで戦い続ける</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.cool.normal[2]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">titleLoss.cool.normal[2]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6939,14 +6939,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しい。だが、糧にはなった。次だ</t>
+          <t xml:space="preserve">…悔しい。チャンピオンとして、もっとやれたはずだ</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.cool.normal[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[2]</t>
+          <t xml:space="preserve">titleWin.cool.normal[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6971,14 +6971,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…実力が足りなかった。強くなって戻る</t>
+          <t xml:space="preserve">…獲った。チャンピオンだ</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.cool.normal[2]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6988,12 +6988,12 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">titleWin.cool.normal[2]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7003,14 +7003,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…防衛。…だが、まだ足りない</t>
+          <t xml:space="preserve">…このベルトは手放さない</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[2]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7035,14 +7035,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…守るたびに、このベルトの重さがわかる</t>
+          <t xml:space="preserve">……そうか。お世話になった</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7052,12 +7052,12 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7067,14 +7067,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…失った。だが、ここで戦い続ける</t>
+          <t xml:space="preserve">……ここでの経験は、忘れない</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[2]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7099,14 +7099,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しい。チャンピオンとして、もっとやれたはずだ</t>
+          <t xml:space="preserve">…レンタルだが、手は抜かない。よろしく</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7131,14 +7131,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…獲った。チャンピオンだ</t>
+          <t xml:space="preserve">…短い間だ。よろしく</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.cool.normal[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[2]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7163,14 +7163,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…このベルトは手放さない</t>
+          <t xml:space="preserve">…悔しい。だが、糧にはなった。次だ</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7180,29 +7180,29 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…相容れない</t>
+          <t xml:space="preserve">…実力が足りなかった。強くなって戻る</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7212,29 +7212,29 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">距離感が…変わった</t>
+          <t xml:space="preserve">…防衛。…だが、まだ足りない</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7244,29 +7244,29 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いいバランスだ。やりやすい</t>
+          <t xml:space="preserve">…守るたびに、このベルトの重さがわかる</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7276,29 +7276,29 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">唯一の、本当の仲間だ</t>
+          <t xml:space="preserve">…失った。だが、ここで戦い続ける</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7308,29 +7308,29 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…執着は、消えたか</t>
+          <t xml:space="preserve">…悔しい。チャンピオンとして、もっとやれたはずだ</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7340,29 +7340,29 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この存在が…引っかかる</t>
+          <t xml:space="preserve">…獲った。チャンピオンだ</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.cool[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7372,29 +7372,29 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.normal.cool[1]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">倒すまで、止まれない</t>
+          <t xml:space="preserve">…このベルトは手放さない</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.cool[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.normal.cool[1]</t>
+          <t xml:space="preserve">bond_39_down.normal.cool[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7419,14 +7419,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着をつけるまで、死んでも死にきれない</t>
+          <t xml:space="preserve">…相容れない</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.cool[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.normal.cool[1]</t>
+          <t xml:space="preserve">bond_59_down.normal.cool[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7451,14 +7451,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここが…自分の場所だ</t>
+          <t xml:space="preserve">距離感が…変わった</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.cool[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.normal.cool[1]</t>
+          <t xml:space="preserve">bond_60_up.normal.cool[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7483,14 +7483,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここにいる理由が…もうない</t>
+          <t xml:space="preserve">いいバランスだ。やりやすい</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.cool[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.cool[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.normal.cool[1]</t>
+          <t xml:space="preserve">bond_80_up.normal.cool[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7515,14 +7515,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この環境に…疑問を感じ始めている</t>
+          <t xml:space="preserve">唯一の、本当の仲間だ</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.cool[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7532,12 +7532,12 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.cool.normal[1]</t>
+          <t xml:space="preserve">rivalry_29_down.normal.cool[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7547,14 +7547,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負けた。だが、後悔はない</t>
+          <t xml:space="preserve">…執着は、消えたか</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.cool[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7564,12 +7564,12 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.cool.normal[1]</t>
+          <t xml:space="preserve">rivalry_30_up.normal.cool[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7579,14 +7579,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……完璧だった</t>
+          <t xml:space="preserve">この存在が…引っかかる</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.cool[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.cool.normal[1]</t>
+          <t xml:space="preserve">rivalry_50_up.normal.cool[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7611,14 +7611,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……足りないか</t>
+          <t xml:space="preserve">倒すまで、止まれない</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.cool[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.cool.normal[1]</t>
+          <t xml:space="preserve">rivalry_70_up.normal.cool[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7643,14 +7643,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った。それでいい</t>
+          <t xml:space="preserve">決着をつけるまで、死んでも死にきれない</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.cool[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7660,12 +7660,12 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.cool.normal[1]</t>
+          <t xml:space="preserve">trust_above_75.normal.cool[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7675,14 +7675,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……集中。あと一セット</t>
+          <t xml:space="preserve">ここが…自分の場所だ</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.cool[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7692,12 +7692,12 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.cool.normal[1]</t>
+          <t xml:space="preserve">trust_below_20.normal.cool[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7707,14 +7707,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この状況は、よくない</t>
+          <t xml:space="preserve">ここにいる理由が…もうない</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.cool[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7724,12 +7724,12 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.cool.normal[1]</t>
+          <t xml:space="preserve">trust_below_35.normal.cool[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7739,14 +7739,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この環境は、悪くない</t>
+          <t xml:space="preserve">この環境に…疑問を感じ始めている</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.cool.normal[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.cool.normal[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.cool.normal[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7771,14 +7771,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…おかげで、ここにいる意味がある</t>
+          <t xml:space="preserve">……負けた。だが、後悔はない</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.cool.normal[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.cool.normal[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.cool.normal[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7803,14 +7803,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……情報は、自然と入ってくる</t>
+          <t xml:space="preserve">……完璧だった</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.cool.normal[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7825,7 +7825,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.cool.normal[1]</t>
+          <t xml:space="preserve">GL-01.loss.cool.normal[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7835,14 +7835,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……出番がないのは、つらい</t>
+          <t xml:space="preserve">……足りないか</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.cool.normal[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.cool.normal[1]</t>
+          <t xml:space="preserve">GL-01.win.cool.normal[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7867,14 +7867,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……体が鈍い。これは…まずいな</t>
+          <t xml:space="preserve">……勝った。それでいい</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.cool.normal[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.cool.normal[1]</t>
+          <t xml:space="preserve">GL-02.cool.normal[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7899,14 +7899,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝てない。何が足りない</t>
+          <t xml:space="preserve">……集中。あと一セット</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.cool.normal[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.cool.normal[1]</t>
+          <t xml:space="preserve">GL-03.down.cool.normal[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7931,14 +7931,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負ける気がしない</t>
+          <t xml:space="preserve">……この状況は、よくない</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.cool.normal[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.cool.normal[1]</t>
+          <t xml:space="preserve">GL-03.up.cool.normal[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7963,14 +7963,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……じっとしているのが、一番つらい</t>
+          <t xml:space="preserve">……この環境は、悪くない</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.cool.normal[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.cool.normal[1]</t>
+          <t xml:space="preserve">GL-04.cool.normal[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -7995,14 +7995,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……認識の外。それだけ</t>
+          <t xml:space="preserve">…おかげで、ここにいる意味がある</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.cool.normal[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8012,12 +8012,12 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">GL-05.cool.normal[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8027,14 +8027,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">調子は戻った。だが…確実に何かを掴んだ</t>
+          <t xml:space="preserve">……情報は、自然と入ってくる</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.cool.normal[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8044,29 +8044,29 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.cool.normal[1]</t>
+          <t xml:space="preserve">GL-06.cool.normal[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…身体の感覚は薄い。それでも、立てる。十分</t>
+          <t xml:space="preserve">……出番がないのは、つらい</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.cool.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.cool.normal[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8076,29 +8076,29 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.cool.normal[2]</t>
+          <t xml:space="preserve">GL-07.cool.normal[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最後の一戦。ここまで来た。降りない</t>
+          <t xml:space="preserve">……体が鈍い。これは…まずいな</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.cool.normal[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8108,29 +8108,29 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.cool.normal[1]</t>
+          <t xml:space="preserve">GL-08.cool.normal[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…相手は誰でもいい</t>
+          <t xml:space="preserve">……勝てない。何が足りない</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.cool.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.cool.normal[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8140,29 +8140,29 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.cool.normal[2]</t>
+          <t xml:space="preserve">GL-09.cool.normal[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">真っ向から受ける。それだけ</t>
+          <t xml:space="preserve">……負ける気がしない</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.cool.normal[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8172,29 +8172,29 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.cool.normal[1]</t>
+          <t xml:space="preserve">GL-10.cool.normal[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一人、落とした。息は上がってる。だが、退かない。次</t>
+          <t xml:space="preserve">……じっとしているのが、一番つらい</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.cool.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.cool.normal[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8204,29 +8204,29 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.cool.normal[2]</t>
+          <t xml:space="preserve">GL-11.cool.normal[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ立ってる。それで十分。次を出せ</t>
+          <t xml:space="preserve">……認識の外。それだけ</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8236,29 +8236,29 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.cool.normal[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人の勝利。それ以上でも以下でもない</t>
+          <t xml:space="preserve">調子は戻った。だが…確実に何かを掴んだ</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.cool.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.cool.normal[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8268,12 +8268,12 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.cool.normal[2]</t>
+          <t xml:space="preserve">preFinal.cool.normal[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8283,14 +8283,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人では成し得なかった。事実としてそう言える</t>
+          <t xml:space="preserve">…身体の感覚は薄い。それでも、立てる。十分</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.cool.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.cool.normal[2]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.cool.normal[1]</t>
+          <t xml:space="preserve">preFinal.cool.normal[2]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8315,14 +8315,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">個人賞は事実として受け取る。だが、団体は負けた。次がある</t>
+          <t xml:space="preserve">…最後の一戦。ここまで来た。降りない</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.cool.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.cool.normal[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8332,12 +8332,12 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.cool.normal[2]</t>
+          <t xml:space="preserve">preMatch.cool.normal[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8347,14 +8347,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足りなかった。それだけ。次で取り返す</t>
+          <t xml:space="preserve">…相手は誰でもいい</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.cool.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.cool.normal[2]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8364,12 +8364,12 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.cool.normal[1]</t>
+          <t xml:space="preserve">preMatch.cool.normal[2]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8379,14 +8379,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体の感覚はとっくに消えてる。それでも足だけは動いた。理由は知らない</t>
+          <t xml:space="preserve">真っ向から受ける。それだけ</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.cool.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.cool.normal[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8396,12 +8396,12 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.cool.normal[2]</t>
+          <t xml:space="preserve">survivor.cool.normal[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8411,14 +8411,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人抜いたかより、最後に立っていたことだけが事実</t>
+          <t xml:space="preserve">…一人、落とした。息は上がってる。だが、退かない。次</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.cool.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.cool.normal[2]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.cool.normal[1]</t>
+          <t xml:space="preserve">survivor.cool.normal[2]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8443,14 +8443,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……優勝。……次のステージへ</t>
+          <t xml:space="preserve">…まだ立ってる。それで十分。次を出せ</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.cool.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.cool.normal[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8460,12 +8460,12 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.cool.normal[2]</t>
+          <t xml:space="preserve">champion.cool.normal[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8475,14 +8475,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとう</t>
+          <t xml:space="preserve">三人の勝利。それ以上でも以下でもない</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.cool.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.cool.normal[2]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.cool.normal[1]</t>
+          <t xml:space="preserve">champion.cool.normal[2]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8507,14 +8507,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ足りない</t>
+          <t xml:space="preserve">一人では成し得なかった。事実としてそう言える</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.cool.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.cool.normal[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8524,12 +8524,12 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.cool.normal[2]</t>
+          <t xml:space="preserve">defiant.cool.normal[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8539,14 +8539,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は負けない</t>
+          <t xml:space="preserve">個人賞は事実として受け取る。だが、団体は負けた。次がある</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.cool.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.cool.normal[2]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.cool.normal[1]</t>
+          <t xml:space="preserve">defiant.cool.normal[2]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8571,14 +8571,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一勝。次</t>
+          <t xml:space="preserve">足りなかった。それだけ。次で取り返す</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.cool.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.cool.normal[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.cool.normal[2]</t>
+          <t xml:space="preserve">gauntlet.cool.normal[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8603,14 +8603,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだだ</t>
+          <t xml:space="preserve">身体の感覚はとっくに消えてる。それでも足だけは動いた。理由は知らない</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.cool.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.cool.normal[2]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8620,12 +8620,12 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.cool.normal[1]</t>
+          <t xml:space="preserve">gauntlet.cool.normal[2]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8635,14 +8635,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悪くなかった</t>
+          <t xml:space="preserve">何人抜いたかより、最後に立っていたことだけが事実</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.cool.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.cool.normal[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.cool.normal[2]</t>
+          <t xml:space="preserve">champion.cool.normal[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8667,14 +8667,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……収穫はあった</t>
+          <t xml:space="preserve">……優勝。……次のステージへ</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.cool.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.cool.normal[2]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8689,7 +8689,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.cool.normal[1]</t>
+          <t xml:space="preserve">champion.cool.normal[2]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8699,14 +8699,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……決勝。全て出す</t>
+          <t xml:space="preserve">……ありがとう</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.cool.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.cool.normal[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.cool.normal[2]</t>
+          <t xml:space="preserve">postLose.cool.normal[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8731,14 +8731,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……最後の一戦</t>
+          <t xml:space="preserve">……まだ足りない</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.cool.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.cool.normal[2]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.cool.normal[1]</t>
+          <t xml:space="preserve">postLose.cool.normal[2]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8763,14 +8763,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……集中する</t>
+          <t xml:space="preserve">……次は負けない</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.cool.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.cool.normal[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.cool.normal[2]</t>
+          <t xml:space="preserve">postMatchWin.cool.normal[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8795,14 +8795,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……行く</t>
+          <t xml:space="preserve">……一勝。次</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.cool.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.cool.normal[2]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8817,7 +8817,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.cool.normal[1]</t>
+          <t xml:space="preserve">postMatchWin.cool.normal[2]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8827,14 +8827,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……出る。それだけだ</t>
+          <t xml:space="preserve">……まだだ</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.cool.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.cool.normal[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.cool.normal[2]</t>
+          <t xml:space="preserve">postWin.cool.normal[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8859,14 +8859,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝つだけだ</t>
+          <t xml:space="preserve">……悪くなかった</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.cool.normal[2]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">postWin.cool.normal[2]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8891,14 +8891,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……受けて立つ。全力だ</t>
+          <t xml:space="preserve">……収穫はあった</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.cool.normal[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">preFinal.cool.normal[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8923,14 +8923,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここが頂点。……でも、まだ先がある</t>
+          <t xml:space="preserve">……決勝。全て出す</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.cool.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.cool.normal[2]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[2]</t>
+          <t xml:space="preserve">preFinal.cool.normal[2]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8955,14 +8955,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った。（静かにベルトを掲げる）</t>
+          <t xml:space="preserve">……最後の一戦</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.cool.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.cool.normal[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">preMatch.cool.normal[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -8987,14 +8987,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……挑戦する。受けろ</t>
+          <t xml:space="preserve">……集中する</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.cool.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.cool.normal[2]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[2]</t>
+          <t xml:space="preserve">preMatch.cool.normal[2]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9019,14 +9019,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……実力で語る。それだけだ</t>
+          <t xml:space="preserve">……行く</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.cool.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.cool.normal[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">summon.cool.normal[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9051,14 +9051,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……臆病者</t>
+          <t xml:space="preserve">……出る。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.cool.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.cool.normal[2]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9068,12 +9068,12 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[2]</t>
+          <t xml:space="preserve">summon.cool.normal[2]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9083,14 +9083,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……逃げたか</t>
+          <t xml:space="preserve">……勝つだけだ</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.cool.normal[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9100,12 +9100,12 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.cool.normal[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9115,14 +9115,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負けた。……受け止める</t>
+          <t xml:space="preserve">……受けて立つ。全力だ</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.cool.normal[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9132,12 +9132,12 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.cool.normal[2]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9147,14 +9147,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は違う</t>
+          <t xml:space="preserve">……ここが頂点。……でも、まだ先がある</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.cool.normal[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.cool.normal[1]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9179,14 +9179,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った。それが全てだ</t>
+          <t xml:space="preserve">……勝った。（静かにベルトを掲げる）</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.cool.normal[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.cool.normal[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.cool.normal[2]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9211,14 +9211,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悪くない</t>
+          <t xml:space="preserve">……挑戦する。受けろ</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.cool.normal[2]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9243,14 +9243,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…団体の看板、背負えた</t>
+          <t xml:space="preserve">……実力で語る。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.cool.normal[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.cool.normal[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9260,12 +9260,12 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[2]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9275,14 +9275,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝った。それだけ</t>
+          <t xml:space="preserve">……臆病者</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.cool.normal[3]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.cool.normal[2]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[3]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9307,14 +9307,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った。それでいい</t>
+          <t xml:space="preserve">……逃げたか</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.cool.normal[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.cool.normal[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9324,29 +9324,29 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.cool.normal[1]</t>
+          <t xml:space="preserve">result_lose.cool.normal[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……終わったか。……悪くない</t>
+          <t xml:space="preserve">……負けた。……受け止める</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.cool.normal[2]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9356,29 +9356,29 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">result_lose.cool.normal[2]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…契約は契約。きっちり働く</t>
+          <t xml:space="preserve">……次は違う</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.cool.normal[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9388,59 +9388,283 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">result_win.cool.normal[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…話は受けた。あとは試合で</t>
+          <t xml:space="preserve">……勝った。それが全てだ</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.cool.normal[2]</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.cool.normal[2]</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……悪くない</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="40" customHeight="1">
+      <c r="A286" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.cool.normal[1]</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cool.normal[1]</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…団体の看板、背負えた</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="40" customHeight="1">
+      <c r="A287" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.cool.normal[2]</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cool.normal[2]</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…勝った。それだけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="40" customHeight="1">
+      <c r="A288" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.cool.normal[3]</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cool.normal[3]</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……勝った。それでいい</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="40" customHeight="1">
+      <c r="A289" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.cool.normal[1]</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.cool.normal[1]</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……終わったか。……悪くない</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="40" customHeight="1">
+      <c r="A290" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.cool.normal[1]</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cool.normal[1]</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…契約は契約。きっちり働く</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="40" customHeight="1">
+      <c r="A291" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.cool.normal[1]</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cool.normal[1]</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…話は受けた。あとは試合で</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="40" customHeight="1">
+      <c r="A292" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.cool.normal[2]</t>
         </is>
       </c>
-      <c r="B285" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr" s="2">
+      <c r="B292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr" s="12">
+      <c r="D292" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
-      <c r="E285" t="inlineStr" s="2">
+      <c r="E292" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F285" t="inlineStr" s="3">
+      <c r="F292" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…期待は、悪くない</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H285"/>
+  <autoFilter ref="A1:H292"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/クール×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/クール×ノーマル.xlsx
@@ -296,7 +296,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H285"/>
+  <dimension ref="A1:H286"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -7650,7 +7650,7 @@
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02-hostile.cool.normal[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7665,7 +7665,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.cool.normal[1]</t>
+          <t xml:space="preserve">GL-02-hostile.cool.normal[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7675,14 +7675,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……集中。あと一セット</t>
+          <t xml:space="preserve">……集中を乱す存在がいる。気に入らない</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.cool.normal[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7697,7 +7697,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.cool.normal[1]</t>
+          <t xml:space="preserve">GL-02.cool.normal[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7707,14 +7707,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この状況は、よくない</t>
+          <t xml:space="preserve">……集中。あと一セット</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.cool.normal[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.cool.normal[1]</t>
+          <t xml:space="preserve">GL-03.down.cool.normal[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7739,14 +7739,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この環境は、悪くない</t>
+          <t xml:space="preserve">……この状況は、よくない</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.cool.normal[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.cool.normal[1]</t>
+          <t xml:space="preserve">GL-03.up.cool.normal[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7771,14 +7771,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…おかげで、ここにいる意味がある</t>
+          <t xml:space="preserve">……この環境は、悪くない</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.cool.normal[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.cool.normal[1]</t>
+          <t xml:space="preserve">GL-04.cool.normal[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7803,14 +7803,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……情報は、自然と入ってくる</t>
+          <t xml:space="preserve">…おかげで、ここにいる意味がある</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.cool.normal[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7825,7 +7825,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.cool.normal[1]</t>
+          <t xml:space="preserve">GL-05.cool.normal[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7835,14 +7835,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……出番がないのは、つらい</t>
+          <t xml:space="preserve">……情報は、自然と入ってくる</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.cool.normal[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.cool.normal[1]</t>
+          <t xml:space="preserve">GL-06.cool.normal[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7867,14 +7867,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……体が鈍い。これは…まずいな</t>
+          <t xml:space="preserve">……出番がないのは、つらい</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.cool.normal[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.cool.normal[1]</t>
+          <t xml:space="preserve">GL-07.cool.normal[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7899,14 +7899,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝てない。何が足りない</t>
+          <t xml:space="preserve">……体が鈍い。これは…まずいな</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.cool.normal[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.cool.normal[1]</t>
+          <t xml:space="preserve">GL-08.cool.normal[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7931,14 +7931,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負ける気がしない</t>
+          <t xml:space="preserve">……勝てない。何が足りない</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.cool.normal[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.cool.normal[1]</t>
+          <t xml:space="preserve">GL-09.cool.normal[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7963,14 +7963,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……じっとしているのが、一番つらい</t>
+          <t xml:space="preserve">……負ける気がしない</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.cool.normal[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.cool.normal[1]</t>
+          <t xml:space="preserve">GL-10.cool.normal[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -7995,14 +7995,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……認識の外。それだけ</t>
+          <t xml:space="preserve">……じっとしているのが、一番つらい</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.cool.normal[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8012,12 +8012,12 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">GL-11.cool.normal[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8027,14 +8027,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">調子は戻った。だが…確実に何かを掴んだ</t>
+          <t xml:space="preserve">……認識の外。それだけ</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.cool.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8044,29 +8044,29 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.cool.normal[1]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…身体の感覚は薄い。それでも、立てる。十分</t>
+          <t xml:space="preserve">調子は戻った。だが…確実に何かを掴んだ</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.cool.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.cool.normal[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.cool.normal[2]</t>
+          <t xml:space="preserve">preFinal.cool.normal[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8091,14 +8091,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最後の一戦。ここまで来た。降りない</t>
+          <t xml:space="preserve">…身体の感覚は薄い。それでも、立てる。十分</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.cool.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.cool.normal[2]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.cool.normal[1]</t>
+          <t xml:space="preserve">preFinal.cool.normal[2]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8123,14 +8123,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…相手は誰でもいい</t>
+          <t xml:space="preserve">…最後の一戦。ここまで来た。降りない</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.cool.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.cool.normal[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.cool.normal[2]</t>
+          <t xml:space="preserve">preMatch.cool.normal[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8155,14 +8155,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">真っ向から受ける。それだけ</t>
+          <t xml:space="preserve">…相手は誰でもいい</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.cool.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.cool.normal[2]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8177,7 +8177,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.cool.normal[1]</t>
+          <t xml:space="preserve">preMatch.cool.normal[2]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8187,14 +8187,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一人、落とした。息は上がってる。だが、退かない。次</t>
+          <t xml:space="preserve">真っ向から受ける。それだけ</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.cool.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.cool.normal[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.cool.normal[2]</t>
+          <t xml:space="preserve">survivor.cool.normal[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8219,14 +8219,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ立ってる。それで十分。次を出せ</t>
+          <t xml:space="preserve">…一人、落とした。息は上がってる。だが、退かない。次</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.cool.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.cool.normal[2]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8236,12 +8236,12 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.cool.normal[1]</t>
+          <t xml:space="preserve">survivor.cool.normal[2]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8251,14 +8251,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人の勝利。それ以上でも以下でもない</t>
+          <t xml:space="preserve">…まだ立ってる。それで十分。次を出せ</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.cool.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.cool.normal[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.cool.normal[2]</t>
+          <t xml:space="preserve">champion.cool.normal[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8283,14 +8283,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人では成し得なかった。事実としてそう言える</t>
+          <t xml:space="preserve">三人の勝利。それ以上でも以下でもない</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.cool.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.cool.normal[2]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.cool.normal[1]</t>
+          <t xml:space="preserve">champion.cool.normal[2]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8315,14 +8315,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">個人賞は事実として受け取る。だが、団体は負けた。次がある</t>
+          <t xml:space="preserve">一人では成し得なかった。事実としてそう言える</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.cool.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.cool.normal[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.cool.normal[2]</t>
+          <t xml:space="preserve">defiant.cool.normal[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8347,14 +8347,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足りなかった。それだけ。次で取り返す</t>
+          <t xml:space="preserve">個人賞は事実として受け取る。だが、団体は負けた。次がある</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.cool.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.cool.normal[2]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8369,7 +8369,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.cool.normal[1]</t>
+          <t xml:space="preserve">defiant.cool.normal[2]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8379,14 +8379,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体の感覚はとっくに消えてる。それでも足だけは動いた。理由は知らない</t>
+          <t xml:space="preserve">足りなかった。それだけ。次で取り返す</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.cool.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.cool.normal[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8401,7 +8401,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.cool.normal[2]</t>
+          <t xml:space="preserve">gauntlet.cool.normal[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8411,14 +8411,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人抜いたかより、最後に立っていたことだけが事実</t>
+          <t xml:space="preserve">身体の感覚はとっくに消えてる。それでも足だけは動いた。理由は知らない</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.cool.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.cool.normal[2]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.cool.normal[1]</t>
+          <t xml:space="preserve">gauntlet.cool.normal[2]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8443,14 +8443,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……優勝。……次のステージへ</t>
+          <t xml:space="preserve">何人抜いたかより、最後に立っていたことだけが事実</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.cool.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.cool.normal[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8465,7 +8465,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.cool.normal[2]</t>
+          <t xml:space="preserve">champion.cool.normal[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8475,14 +8475,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとう</t>
+          <t xml:space="preserve">……優勝。……次のステージへ</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.cool.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.cool.normal[2]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8497,7 +8497,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.cool.normal[1]</t>
+          <t xml:space="preserve">champion.cool.normal[2]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8507,14 +8507,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ足りない</t>
+          <t xml:space="preserve">……ありがとう</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.cool.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.cool.normal[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8529,7 +8529,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.cool.normal[2]</t>
+          <t xml:space="preserve">postLose.cool.normal[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8539,14 +8539,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は負けない</t>
+          <t xml:space="preserve">……まだ足りない</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.cool.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.cool.normal[2]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.cool.normal[1]</t>
+          <t xml:space="preserve">postLose.cool.normal[2]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8571,14 +8571,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一勝。次</t>
+          <t xml:space="preserve">……次は負けない</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.cool.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.cool.normal[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8593,7 +8593,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.cool.normal[2]</t>
+          <t xml:space="preserve">postMatchWin.cool.normal[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8603,14 +8603,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだだ</t>
+          <t xml:space="preserve">……一勝。次</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.cool.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.cool.normal[2]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.cool.normal[1]</t>
+          <t xml:space="preserve">postMatchWin.cool.normal[2]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8635,14 +8635,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悪くなかった</t>
+          <t xml:space="preserve">……まだだ</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.cool.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.cool.normal[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.cool.normal[2]</t>
+          <t xml:space="preserve">postWin.cool.normal[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8667,14 +8667,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……収穫はあった</t>
+          <t xml:space="preserve">……悪くなかった</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.cool.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.cool.normal[2]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8689,7 +8689,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.cool.normal[1]</t>
+          <t xml:space="preserve">postWin.cool.normal[2]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8699,14 +8699,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……決勝。全て出す</t>
+          <t xml:space="preserve">……収穫はあった</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.cool.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.cool.normal[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.cool.normal[2]</t>
+          <t xml:space="preserve">preFinal.cool.normal[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8731,14 +8731,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……最後の一戦</t>
+          <t xml:space="preserve">……決勝。全て出す</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.cool.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.cool.normal[2]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.cool.normal[1]</t>
+          <t xml:space="preserve">preFinal.cool.normal[2]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8763,14 +8763,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……集中する</t>
+          <t xml:space="preserve">……最後の一戦</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.cool.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.cool.normal[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.cool.normal[2]</t>
+          <t xml:space="preserve">preMatch.cool.normal[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8795,14 +8795,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……行く</t>
+          <t xml:space="preserve">……集中する</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.cool.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.cool.normal[2]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8817,7 +8817,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.cool.normal[1]</t>
+          <t xml:space="preserve">preMatch.cool.normal[2]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8827,14 +8827,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……出る。それだけだ</t>
+          <t xml:space="preserve">……行く</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.cool.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.cool.normal[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.cool.normal[2]</t>
+          <t xml:space="preserve">summon.cool.normal[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8859,14 +8859,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝つだけだ</t>
+          <t xml:space="preserve">……出る。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.cool.normal[2]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">summon.cool.normal[2]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8891,14 +8891,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……受けて立つ。全力だ</t>
+          <t xml:space="preserve">……勝つだけだ</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8908,7 +8908,7 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
@@ -8923,14 +8923,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここが頂点。……でも、まだ先がある</t>
+          <t xml:space="preserve">……受けて立つ。全力だ</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.cool.normal[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8945,7 +8945,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[2]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8955,14 +8955,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った。（静かにベルトを掲げる）</t>
+          <t xml:space="preserve">……ここが頂点。……でも、まだ先がある</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.cool.normal[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -8987,14 +8987,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……挑戦する。受けろ</t>
+          <t xml:space="preserve">……勝った。（静かにベルトを掲げる）</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.cool.normal[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.cool.normal[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9009,7 +9009,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[2]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9019,14 +9019,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……実力で語る。それだけだ</t>
+          <t xml:space="preserve">……挑戦する。受けろ</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.cool.normal[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.cool.normal[2]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9051,14 +9051,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……臆病者</t>
+          <t xml:space="preserve">……実力で語る。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.cool.normal[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.cool.normal[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[2]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9083,14 +9083,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……逃げたか</t>
+          <t xml:space="preserve">……臆病者</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.cool.normal[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.cool.normal[2]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9100,12 +9100,12 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.cool.normal[1]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9115,14 +9115,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負けた。……受け止める</t>
+          <t xml:space="preserve">……逃げたか</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.cool.normal[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.cool.normal[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9137,7 +9137,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.cool.normal[2]</t>
+          <t xml:space="preserve">result_lose.cool.normal[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9147,14 +9147,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は違う</t>
+          <t xml:space="preserve">……負けた。……受け止める</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.cool.normal[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.cool.normal[2]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.cool.normal[1]</t>
+          <t xml:space="preserve">result_lose.cool.normal[2]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9179,14 +9179,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った。それが全てだ</t>
+          <t xml:space="preserve">……次は違う</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.cool.normal[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.cool.normal[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.cool.normal[2]</t>
+          <t xml:space="preserve">result_win.cool.normal[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9211,14 +9211,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悪くない</t>
+          <t xml:space="preserve">……勝った。それが全てだ</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.cool.normal[2]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">result_win.cool.normal[2]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9243,14 +9243,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…団体の看板、背負えた</t>
+          <t xml:space="preserve">……悪くない</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.cool.normal[2]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9265,7 +9265,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[2]</t>
+          <t xml:space="preserve">cool.normal[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9275,14 +9275,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝った。それだけ</t>
+          <t xml:space="preserve">…団体の看板、背負えた</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.cool.normal[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.cool.normal[2]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9297,7 +9297,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[3]</t>
+          <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9307,14 +9307,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った。それでいい</t>
+          <t xml:space="preserve">…勝った。それだけ</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.cool.normal[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.cool.normal[3]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9324,29 +9324,29 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.cool.normal[1]</t>
+          <t xml:space="preserve">cool.normal[3]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……終わったか。……悪くない</t>
+          <t xml:space="preserve">……勝った。それでいい</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.cool.normal[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9356,29 +9356,29 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool.normal[1]</t>
+          <t xml:space="preserve">fighter.cool.normal[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…契約は契約。きっちり働く</t>
+          <t xml:space="preserve">……終わったか。……悪くない</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.cool.normal[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.cool.normal[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9388,7 +9388,7 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
@@ -9403,44 +9403,76 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…話は受けた。あとは試合で</t>
+          <t xml:space="preserve">…契約は契約。きっちり働く</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.cool.normal[1]</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cool.normal[1]</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…話は受けた。あとは試合で</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="40" customHeight="1">
+      <c r="A286" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.cool.normal[2]</t>
         </is>
       </c>
-      <c r="B285" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr" s="2">
+      <c r="B286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr" s="12">
+      <c r="D286" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">cool.normal[2]</t>
         </is>
       </c>
-      <c r="E285" t="inlineStr" s="2">
+      <c r="E286" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F285" t="inlineStr" s="3">
+      <c r="F286" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…期待は、悪くない</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H285"/>
+  <autoFilter ref="A1:H286"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/クール×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/クール×ノーマル.xlsx
@@ -2459,7 +2459,7 @@
       </c>
       <c r="F67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……社長。あの人と、やらせてください。</t>
+          <t xml:space="preserve">……社長。三人で、あちらへ行かせてください。</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="F68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……頼みがあります。あの人と、やりたい。</t>
+          <t xml:space="preserve">……頼みがあります。三人で、あの団体へ行きたい。</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="F69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの人だ。あの人と、やらせてほしい。</t>
+          <t xml:space="preserve">……あの団体だ。三人で乗り込ませてほしい。</t>
         </is>
       </c>
     </row>
